--- a/AI-GTM-OS-API-Acquisition.xlsx
+++ b/AI-GTM-OS-API-Acquisition.xlsx
@@ -15,8 +15,8 @@
     <sheet name=".env Key Map" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'API Master List'!$A$1:$U$68</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'.env Key Map'!$A$4:$E$197</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'API Master List'!$A$1:$U$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'.env Key Map'!$A$4:$E$208</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -931,7 +931,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Anthropic only. ~$50 of credits and every one of the 38 agents starts reasoning for real.</t>
+          <t>A Groq API key. Free tier works for testing; every one of the 38 agents starts reasoning for real.</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>≈ $375/month of software gets the entire P0 + P1 loop running live on real data — Claude, Apollo, a verifier, Instantly, HubSpot, Stripe, GA4 and Google Ads. The ad budget itself is separate and will be the larger number. See the Cost Model sheet.</t>
+          <t>≈ $375/month of software gets the entire P0 + P1 loop running live on real data — Groq, Apollo, a verifier, Instantly, HubSpot, Stripe, GA4 and Google Ads. The ad budget itself is separate and will be the larger number. See the Cost Model sheet.</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U68"/>
+  <dimension ref="A1:U69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="D2" s="11" t="inlineStr">
         <is>
-          <t>Anthropic (Claude)</t>
+          <t>Groq</t>
         </is>
       </c>
       <c r="E2" s="10" t="inlineStr">
@@ -1259,45 +1259,45 @@
       </c>
       <c r="I2" s="10" t="inlineStr">
         <is>
-          <t>Email + card</t>
+          <t>Email (free tier needs no card)</t>
         </is>
       </c>
       <c r="J2" s="10" t="inlineStr">
         <is>
-          <t>Prepaid credits, per-token</t>
+          <t>Free tier, then pay-per-token</t>
         </is>
       </c>
       <c r="K2" s="14" t="n">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="L2" s="10" t="inlineStr">
         <is>
-          <t>$5 trial credit</t>
+          <t>Yes - free tier, rate-limited</t>
         </is>
       </c>
       <c r="M2" s="15" t="inlineStr">
         <is>
-          <t>https://console.anthropic.com/settings/keys</t>
+          <t>https://console.groq.com/keys</t>
         </is>
       </c>
       <c r="N2" s="15" t="inlineStr">
         <is>
-          <t>https://docs.anthropic.com</t>
+          <t>https://console.groq.com/docs</t>
         </is>
       </c>
       <c r="O2" s="10" t="inlineStr">
         <is>
-          <t>1) Sign up at console.anthropic.com. 2) Billing -&gt; add payment method, buy credits ($50 is plenty to start). 3) API Keys -&gt; Create Key -&gt; copy once (shown only once). 4) Paste into ANTHROPIC_API_KEY in .env. 5) Restart Django; the sidebar badge flips from 'Simulation mode' to 'Claude live'. 6) Optional: set a monthly spend limit under Billing -&gt; Limits.</t>
+          <t>1) Sign up at console.groq.com (Google/GitHub login works). 2) API Keys -&gt; Create API Key -&gt; copy it (shown once). 3) Paste into GROQ_API_KEY in .env. 4) Check which models your key can use: curl https://api.groq.com/openai/v1/models -H "Authorization: Bearer $GROQ_API_KEY" 5) Set GROQ_MODEL (reasoning) and GROQ_WORKER_MODEL (bulk/cheap) to IDs from that list. 6) Restart Django - the sidebar badge flips from 'Demo data' to 'AI is live'. 7) For production volume, add billing in the console to lift the free-tier rate limits.</t>
         </is>
       </c>
       <c r="P2" s="10" t="inlineStr">
         <is>
-          <t>ANTHROPIC_API_KEY, ANTHROPIC_MODEL, ANTHROPIC_WORKER_MODEL</t>
+          <t>GROQ_API_KEY, GROQ_MODEL, GROQ_WORKER_MODEL, LLM_PROVIDER</t>
         </is>
       </c>
       <c r="Q2" s="10" t="inlineStr">
         <is>
-          <t>Set a spend limit before you let agents run on a schedule. Workspace-scoped keys let you separate dev/prod.</t>
+          <t>THE FREE TIER IS RATE-LIMITED (requests and tokens per minute) - fine for testing, but running all 38 agents will hit it. The client retries with backoff (GROQ_MAX_RETRIES), but add billing before scheduling agent runs. Model IDs change: verify against the /models endpoint rather than trusting a hardcoded name.</t>
         </is>
       </c>
       <c r="R2" s="10" t="inlineStr">
@@ -7058,17 +7058,17 @@
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Anthropic (Claude)</t>
         </is>
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>Optional secondary model / embeddings</t>
-        </is>
-      </c>
-      <c r="F66" s="24" t="inlineStr">
-        <is>
-          <t>Optional</t>
+          <t>Alternative LLM for every agent (set LLM_PROVIDER=anthropic)</t>
+        </is>
+      </c>
+      <c r="F66" s="19" t="inlineStr">
+        <is>
+          <t>Alternative</t>
         </is>
       </c>
       <c r="G66" s="13" t="inlineStr">
@@ -7083,45 +7083,45 @@
       </c>
       <c r="I66" s="10" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Email + card</t>
         </is>
       </c>
       <c r="J66" s="10" t="inlineStr">
         <is>
-          <t>Per-token</t>
+          <t>Prepaid credits, per-token</t>
         </is>
       </c>
       <c r="K66" s="14" t="n">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="L66" s="10" t="inlineStr">
         <is>
-          <t>None (prepaid)</t>
+          <t>$5 trial credit</t>
         </is>
       </c>
       <c r="M66" s="15" t="inlineStr">
         <is>
-          <t>https://platform.openai.com/api-keys</t>
+          <t>https://console.anthropic.com/settings/keys</t>
         </is>
       </c>
       <c r="N66" s="15" t="inlineStr">
         <is>
-          <t>https://platform.openai.com/docs</t>
+          <t>https://docs.anthropic.com</t>
         </is>
       </c>
       <c r="O66" s="10" t="inlineStr">
         <is>
-          <t>1) Sign up -&gt; Billing -&gt; add credits. 2) API Keys -&gt; create. 3) Paste into OPENAI_API_KEY.</t>
+          <t>1) pip install anthropic. 2) Sign up at console.anthropic.com, add a payment method and buy credits. 3) API Keys -&gt; Create Key -&gt; copy once. 4) Set ANTHROPIC_API_KEY and LLM_PROVIDER=anthropic. 5) Set a monthly spend limit under Billing -&gt; Limits.</t>
         </is>
       </c>
       <c r="P66" s="10" t="inlineStr">
         <is>
-          <t>OPENAI_API_KEY</t>
+          <t>ANTHROPIC_API_KEY, ANTHROPIC_MODEL, ANTHROPIC_WORKER_MODEL, LLM_PROVIDER</t>
         </is>
       </c>
       <c r="Q66" s="10" t="inlineStr">
         <is>
-          <t>Not required — every agent runs on Claude. Only add if you specifically want a second provider for embeddings.</t>
+          <t>Stronger reasoning than the Groq models but roughly 5-10x the cost and much slower per response. Worth testing if agent output quality is the bottleneck. Pick ONE LLM provider.</t>
         </is>
       </c>
       <c r="R66" s="10" t="inlineStr">
@@ -7144,22 +7144,22 @@
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>Creative Generation</t>
+          <t>AI Models</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>Stability AI</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>Creative Director: image generation</t>
-        </is>
-      </c>
-      <c r="F67" s="24" t="inlineStr">
-        <is>
-          <t>Optional</t>
+          <t>Alternative LLM / embeddings (set LLM_PROVIDER=openai)</t>
+        </is>
+      </c>
+      <c r="F67" s="19" t="inlineStr">
+        <is>
+          <t>Alternative</t>
         </is>
       </c>
       <c r="G67" s="13" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="I67" s="10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="J67" s="10" t="inlineStr">
         <is>
-          <t>Credits</t>
+          <t>Per-token</t>
         </is>
       </c>
       <c r="K67" s="14" t="n">
@@ -7187,32 +7187,32 @@
       </c>
       <c r="L67" s="10" t="inlineStr">
         <is>
-          <t>Trial credits</t>
+          <t>None (prepaid)</t>
         </is>
       </c>
       <c r="M67" s="15" t="inlineStr">
         <is>
-          <t>https://platform.stability.ai</t>
+          <t>https://platform.openai.com/api-keys</t>
         </is>
       </c>
       <c r="N67" s="15" t="inlineStr">
         <is>
-          <t>https://platform.stability.ai/docs</t>
+          <t>https://platform.openai.com/docs</t>
         </is>
       </c>
       <c r="O67" s="10" t="inlineStr">
         <is>
-          <t>1) Sign up. 2) Account -&gt; API Keys -&gt; copy. 3) Paste into STABILITY_API_KEY.</t>
+          <t>1) pip install openai. 2) Sign up -&gt; Billing -&gt; add credits. 3) API Keys -&gt; create. 4) Set OPENAI_API_KEY and LLM_PROVIDER=openai. OPENAI_BASE_URL also lets you point at any OpenAI-compatible gateway (Together, OpenRouter, a local vLLM server).</t>
         </is>
       </c>
       <c r="P67" s="10" t="inlineStr">
         <is>
-          <t>STABILITY_API_KEY</t>
+          <t>OPENAI_API_KEY, OPENAI_MODEL, OPENAI_WORKER_MODEL, OPENAI_BASE_URL, LLM_PROVIDER</t>
         </is>
       </c>
       <c r="Q67" s="10" t="inlineStr">
         <is>
-          <t>fal.ai gives you this plus more models behind one key.</t>
+          <t>Not required - the agents run on Groq by default. Pick ONE LLM provider.</t>
         </is>
       </c>
       <c r="R67" s="10" t="inlineStr">
@@ -7235,17 +7235,17 @@
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Creative Generation</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>AWS S3 / Cloudflare R2</t>
+          <t>Stability AI</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>Storage for generated creatives, videos and exports</t>
+          <t>Creative Director: image generation</t>
         </is>
       </c>
       <c r="F68" s="24" t="inlineStr">
@@ -7253,57 +7253,57 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="G68" s="18" t="inlineStr">
-        <is>
-          <t>Easy</t>
+      <c r="G68" s="13" t="inlineStr">
+        <is>
+          <t>Instant</t>
         </is>
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>30 minutes</t>
+          <t>5 minutes</t>
         </is>
       </c>
       <c r="I68" s="10" t="inlineStr">
         <is>
-          <t>AWS or Cloudflare account</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J68" s="10" t="inlineStr">
         <is>
-          <t>Per GB stored + egress</t>
+          <t>Credits</t>
         </is>
       </c>
       <c r="K68" s="14" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L68" s="10" t="inlineStr">
         <is>
-          <t>R2 has free egress</t>
+          <t>Trial credits</t>
         </is>
       </c>
       <c r="M68" s="15" t="inlineStr">
         <is>
-          <t>https://aws.amazon.com/s3/</t>
+          <t>https://platform.stability.ai</t>
         </is>
       </c>
       <c r="N68" s="15" t="inlineStr">
         <is>
-          <t>https://docs.aws.amazon.com/s3/</t>
+          <t>https://platform.stability.ai/docs</t>
         </is>
       </c>
       <c r="O68" s="10" t="inlineStr">
         <is>
-          <t>1) Create a bucket (private). 2) Create an IAM user with least-privilege access to that bucket only. 3) Generate an access key pair. 4) Fill AWS_ACCESS_KEY_ID, AWS_SECRET_ACCESS_KEY, AWS_STORAGE_BUCKET_NAME, AWS_S3_REGION_NAME and set STORAGE_BACKEND=s3.</t>
+          <t>1) Sign up. 2) Account -&gt; API Keys -&gt; copy. 3) Paste into STABILITY_API_KEY.</t>
         </is>
       </c>
       <c r="P68" s="10" t="inlineStr">
         <is>
-          <t>AWS_ACCESS_KEY_ID, AWS_SECRET_ACCESS_KEY, AWS_STORAGE_BUCKET_NAME, AWS_S3_REGION_NAME, STORAGE_BACKEND</t>
+          <t>STABILITY_API_KEY</t>
         </is>
       </c>
       <c r="Q68" s="10" t="inlineStr">
         <is>
-          <t>Local storage is the default and fine until you generate video at volume. R2 avoids egress fees.</t>
+          <t>fal.ai gives you this plus more models behind one key.</t>
         </is>
       </c>
       <c r="R68" s="10" t="inlineStr">
@@ -7315,9 +7315,100 @@
       <c r="T68" s="16" t="inlineStr"/>
       <c r="U68" s="10" t="inlineStr"/>
     </row>
+    <row r="69" ht="96" customHeight="1">
+      <c r="A69" s="8" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="26" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>AWS S3 / Cloudflare R2</t>
+        </is>
+      </c>
+      <c r="E69" s="10" t="inlineStr">
+        <is>
+          <t>Storage for generated creatives, videos and exports</t>
+        </is>
+      </c>
+      <c r="F69" s="24" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="G69" s="18" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="H69" s="10" t="inlineStr">
+        <is>
+          <t>30 minutes</t>
+        </is>
+      </c>
+      <c r="I69" s="10" t="inlineStr">
+        <is>
+          <t>AWS or Cloudflare account</t>
+        </is>
+      </c>
+      <c r="J69" s="10" t="inlineStr">
+        <is>
+          <t>Per GB stored + egress</t>
+        </is>
+      </c>
+      <c r="K69" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="L69" s="10" t="inlineStr">
+        <is>
+          <t>R2 has free egress</t>
+        </is>
+      </c>
+      <c r="M69" s="15" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/s3/</t>
+        </is>
+      </c>
+      <c r="N69" s="15" t="inlineStr">
+        <is>
+          <t>https://docs.aws.amazon.com/s3/</t>
+        </is>
+      </c>
+      <c r="O69" s="10" t="inlineStr">
+        <is>
+          <t>1) Create a bucket (private). 2) Create an IAM user with least-privilege access to that bucket only. 3) Generate an access key pair. 4) Fill AWS_ACCESS_KEY_ID, AWS_SECRET_ACCESS_KEY, AWS_STORAGE_BUCKET_NAME, AWS_S3_REGION_NAME and set STORAGE_BACKEND=s3.</t>
+        </is>
+      </c>
+      <c r="P69" s="10" t="inlineStr">
+        <is>
+          <t>AWS_ACCESS_KEY_ID, AWS_SECRET_ACCESS_KEY, AWS_STORAGE_BUCKET_NAME, AWS_S3_REGION_NAME, STORAGE_BACKEND</t>
+        </is>
+      </c>
+      <c r="Q69" s="10" t="inlineStr">
+        <is>
+          <t>Local storage is the default and fine until you generate video at volume. R2 avoids egress fees.</t>
+        </is>
+      </c>
+      <c r="R69" s="10" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="S69" s="10" t="inlineStr"/>
+      <c r="T69" s="16" t="inlineStr"/>
+      <c r="U69" s="10" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U68"/>
-  <conditionalFormatting sqref="R2:R68">
+  <autoFilter ref="A1:U69"/>
+  <conditionalFormatting sqref="R2:R69">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Live"</formula>
     </cfRule>
@@ -7341,7 +7432,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="R2:R68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick a status from the list" type="list">
+    <dataValidation sqref="R2:R69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick a status from the list" type="list">
       <formula1>"Not started,Prereq pending,Applied,In review,Approved,Live,Blocked,Skipped"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7480,6 +7571,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N67" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M68" r:id="rId133"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N69" r:id="rId136"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7572,19 +7665,19 @@
         </is>
       </c>
       <c r="C5" s="30">
-        <f>COUNTIF('API Master List'!$B$2:$B$68,"P0")</f>
+        <f>COUNTIF('API Master List'!$B$2:$B$69,"P0")</f>
         <v/>
       </c>
       <c r="D5" s="30">
-        <f>COUNTIFS('API Master List'!$B$2:$B$68,"P0",'API Master List'!$R$2:$R$68,"Live")</f>
+        <f>COUNTIFS('API Master List'!$B$2:$B$69,"P0",'API Master List'!$R$2:$R$69,"Live")</f>
         <v/>
       </c>
       <c r="E5" s="30">
-        <f>COUNTIFS('API Master List'!$B$2:$B$68,"P0",'API Master List'!$R$2:$R$68,"Applied")+COUNTIFS('API Master List'!$B$2:$B$68,"P0",'API Master List'!$R$2:$R$68,"In review")+COUNTIFS('API Master List'!$B$2:$B$68,"P0",'API Master List'!$R$2:$R$68,"Approved")</f>
+        <f>COUNTIFS('API Master List'!$B$2:$B$69,"P0",'API Master List'!$R$2:$R$69,"Applied")+COUNTIFS('API Master List'!$B$2:$B$69,"P0",'API Master List'!$R$2:$R$69,"In review")+COUNTIFS('API Master List'!$B$2:$B$69,"P0",'API Master List'!$R$2:$R$69,"Approved")</f>
         <v/>
       </c>
       <c r="F5" s="30">
-        <f>COUNTIFS('API Master List'!$B$2:$B$68,"P0",'API Master List'!$R$2:$R$68,"Not started")</f>
+        <f>COUNTIFS('API Master List'!$B$2:$B$69,"P0",'API Master List'!$R$2:$R$69,"Not started")</f>
         <v/>
       </c>
       <c r="G5" s="31">
@@ -7592,7 +7685,7 @@
         <v/>
       </c>
       <c r="H5" s="32">
-        <f>SUMIFS('API Master List'!$K$2:$K$68,'API Master List'!$B$2:$B$68,"P0",'API Master List'!$F$2:$F$68,"Required")+SUMIFS('API Master List'!$K$2:$K$68,'API Master List'!$B$2:$B$68,"P0",'API Master List'!$F$2:$F$68,"Recommended")</f>
+        <f>SUMIFS('API Master List'!$K$2:$K$69,'API Master List'!$B$2:$B$69,"P0",'API Master List'!$F$2:$F$69,"Required")+SUMIFS('API Master List'!$K$2:$K$69,'API Master List'!$B$2:$B$69,"P0",'API Master List'!$F$2:$F$69,"Recommended")</f>
         <v/>
       </c>
     </row>
@@ -7608,19 +7701,19 @@
         </is>
       </c>
       <c r="C6" s="30">
-        <f>COUNTIF('API Master List'!$B$2:$B$68,"P1")</f>
+        <f>COUNTIF('API Master List'!$B$2:$B$69,"P1")</f>
         <v/>
       </c>
       <c r="D6" s="30">
-        <f>COUNTIFS('API Master List'!$B$2:$B$68,"P1",'API Master List'!$R$2:$R$68,"Live")</f>
+        <f>COUNTIFS('API Master List'!$B$2:$B$69,"P1",'API Master List'!$R$2:$R$69,"Live")</f>
         <v/>
       </c>
       <c r="E6" s="30">
-        <f>COUNTIFS('API Master List'!$B$2:$B$68,"P1",'API Master List'!$R$2:$R$68,"Applied")+COUNTIFS('API Master List'!$B$2:$B$68,"P1",'API Master List'!$R$2:$R$68,"In review")+COUNTIFS('API Master List'!$B$2:$B$68,"P1",'API Master List'!$R$2:$R$68,"Approved")</f>
+        <f>COUNTIFS('API Master List'!$B$2:$B$69,"P1",'API Master List'!$R$2:$R$69,"Applied")+COUNTIFS('API Master List'!$B$2:$B$69,"P1",'API Master List'!$R$2:$R$69,"In review")+COUNTIFS('API Master List'!$B$2:$B$69,"P1",'API Master List'!$R$2:$R$69,"Approved")</f>
         <v/>
       </c>
       <c r="F6" s="30">
-        <f>COUNTIFS('API Master List'!$B$2:$B$68,"P1",'API Master List'!$R$2:$R$68,"Not started")</f>
+        <f>COUNTIFS('API Master List'!$B$2:$B$69,"P1",'API Master List'!$R$2:$R$69,"Not started")</f>
         <v/>
       </c>
       <c r="G6" s="31">
@@ -7628,7 +7721,7 @@
         <v/>
       </c>
       <c r="H6" s="32">
-        <f>SUMIFS('API Master List'!$K$2:$K$68,'API Master List'!$B$2:$B$68,"P1",'API Master List'!$F$2:$F$68,"Required")+SUMIFS('API Master List'!$K$2:$K$68,'API Master List'!$B$2:$B$68,"P1",'API Master List'!$F$2:$F$68,"Recommended")</f>
+        <f>SUMIFS('API Master List'!$K$2:$K$69,'API Master List'!$B$2:$B$69,"P1",'API Master List'!$F$2:$F$69,"Required")+SUMIFS('API Master List'!$K$2:$K$69,'API Master List'!$B$2:$B$69,"P1",'API Master List'!$F$2:$F$69,"Recommended")</f>
         <v/>
       </c>
     </row>
@@ -7644,19 +7737,19 @@
         </is>
       </c>
       <c r="C7" s="30">
-        <f>COUNTIF('API Master List'!$B$2:$B$68,"P2")</f>
+        <f>COUNTIF('API Master List'!$B$2:$B$69,"P2")</f>
         <v/>
       </c>
       <c r="D7" s="30">
-        <f>COUNTIFS('API Master List'!$B$2:$B$68,"P2",'API Master List'!$R$2:$R$68,"Live")</f>
+        <f>COUNTIFS('API Master List'!$B$2:$B$69,"P2",'API Master List'!$R$2:$R$69,"Live")</f>
         <v/>
       </c>
       <c r="E7" s="30">
-        <f>COUNTIFS('API Master List'!$B$2:$B$68,"P2",'API Master List'!$R$2:$R$68,"Applied")+COUNTIFS('API Master List'!$B$2:$B$68,"P2",'API Master List'!$R$2:$R$68,"In review")+COUNTIFS('API Master List'!$B$2:$B$68,"P2",'API Master List'!$R$2:$R$68,"Approved")</f>
+        <f>COUNTIFS('API Master List'!$B$2:$B$69,"P2",'API Master List'!$R$2:$R$69,"Applied")+COUNTIFS('API Master List'!$B$2:$B$69,"P2",'API Master List'!$R$2:$R$69,"In review")+COUNTIFS('API Master List'!$B$2:$B$69,"P2",'API Master List'!$R$2:$R$69,"Approved")</f>
         <v/>
       </c>
       <c r="F7" s="30">
-        <f>COUNTIFS('API Master List'!$B$2:$B$68,"P2",'API Master List'!$R$2:$R$68,"Not started")</f>
+        <f>COUNTIFS('API Master List'!$B$2:$B$69,"P2",'API Master List'!$R$2:$R$69,"Not started")</f>
         <v/>
       </c>
       <c r="G7" s="31">
@@ -7664,7 +7757,7 @@
         <v/>
       </c>
       <c r="H7" s="32">
-        <f>SUMIFS('API Master List'!$K$2:$K$68,'API Master List'!$B$2:$B$68,"P2",'API Master List'!$F$2:$F$68,"Required")+SUMIFS('API Master List'!$K$2:$K$68,'API Master List'!$B$2:$B$68,"P2",'API Master List'!$F$2:$F$68,"Recommended")</f>
+        <f>SUMIFS('API Master List'!$K$2:$K$69,'API Master List'!$B$2:$B$69,"P2",'API Master List'!$F$2:$F$69,"Required")+SUMIFS('API Master List'!$K$2:$K$69,'API Master List'!$B$2:$B$69,"P2",'API Master List'!$F$2:$F$69,"Recommended")</f>
         <v/>
       </c>
     </row>
@@ -7680,19 +7773,19 @@
         </is>
       </c>
       <c r="C8" s="30">
-        <f>COUNTIF('API Master List'!$B$2:$B$68,"P3")</f>
+        <f>COUNTIF('API Master List'!$B$2:$B$69,"P3")</f>
         <v/>
       </c>
       <c r="D8" s="30">
-        <f>COUNTIFS('API Master List'!$B$2:$B$68,"P3",'API Master List'!$R$2:$R$68,"Live")</f>
+        <f>COUNTIFS('API Master List'!$B$2:$B$69,"P3",'API Master List'!$R$2:$R$69,"Live")</f>
         <v/>
       </c>
       <c r="E8" s="30">
-        <f>COUNTIFS('API Master List'!$B$2:$B$68,"P3",'API Master List'!$R$2:$R$68,"Applied")+COUNTIFS('API Master List'!$B$2:$B$68,"P3",'API Master List'!$R$2:$R$68,"In review")+COUNTIFS('API Master List'!$B$2:$B$68,"P3",'API Master List'!$R$2:$R$68,"Approved")</f>
+        <f>COUNTIFS('API Master List'!$B$2:$B$69,"P3",'API Master List'!$R$2:$R$69,"Applied")+COUNTIFS('API Master List'!$B$2:$B$69,"P3",'API Master List'!$R$2:$R$69,"In review")+COUNTIFS('API Master List'!$B$2:$B$69,"P3",'API Master List'!$R$2:$R$69,"Approved")</f>
         <v/>
       </c>
       <c r="F8" s="30">
-        <f>COUNTIFS('API Master List'!$B$2:$B$68,"P3",'API Master List'!$R$2:$R$68,"Not started")</f>
+        <f>COUNTIFS('API Master List'!$B$2:$B$69,"P3",'API Master List'!$R$2:$R$69,"Not started")</f>
         <v/>
       </c>
       <c r="G8" s="31">
@@ -7700,7 +7793,7 @@
         <v/>
       </c>
       <c r="H8" s="32">
-        <f>SUMIFS('API Master List'!$K$2:$K$68,'API Master List'!$B$2:$B$68,"P3",'API Master List'!$F$2:$F$68,"Required")+SUMIFS('API Master List'!$K$2:$K$68,'API Master List'!$B$2:$B$68,"P3",'API Master List'!$F$2:$F$68,"Recommended")</f>
+        <f>SUMIFS('API Master List'!$K$2:$K$69,'API Master List'!$B$2:$B$69,"P3",'API Master List'!$F$2:$F$69,"Required")+SUMIFS('API Master List'!$K$2:$K$69,'API Master List'!$B$2:$B$69,"P3",'API Master List'!$F$2:$F$69,"Recommended")</f>
         <v/>
       </c>
     </row>
@@ -7716,19 +7809,19 @@
         </is>
       </c>
       <c r="C9" s="30">
-        <f>COUNTIF('API Master List'!$B$2:$B$68,"P4")</f>
+        <f>COUNTIF('API Master List'!$B$2:$B$69,"P4")</f>
         <v/>
       </c>
       <c r="D9" s="30">
-        <f>COUNTIFS('API Master List'!$B$2:$B$68,"P4",'API Master List'!$R$2:$R$68,"Live")</f>
+        <f>COUNTIFS('API Master List'!$B$2:$B$69,"P4",'API Master List'!$R$2:$R$69,"Live")</f>
         <v/>
       </c>
       <c r="E9" s="30">
-        <f>COUNTIFS('API Master List'!$B$2:$B$68,"P4",'API Master List'!$R$2:$R$68,"Applied")+COUNTIFS('API Master List'!$B$2:$B$68,"P4",'API Master List'!$R$2:$R$68,"In review")+COUNTIFS('API Master List'!$B$2:$B$68,"P4",'API Master List'!$R$2:$R$68,"Approved")</f>
+        <f>COUNTIFS('API Master List'!$B$2:$B$69,"P4",'API Master List'!$R$2:$R$69,"Applied")+COUNTIFS('API Master List'!$B$2:$B$69,"P4",'API Master List'!$R$2:$R$69,"In review")+COUNTIFS('API Master List'!$B$2:$B$69,"P4",'API Master List'!$R$2:$R$69,"Approved")</f>
         <v/>
       </c>
       <c r="F9" s="30">
-        <f>COUNTIFS('API Master List'!$B$2:$B$68,"P4",'API Master List'!$R$2:$R$68,"Not started")</f>
+        <f>COUNTIFS('API Master List'!$B$2:$B$69,"P4",'API Master List'!$R$2:$R$69,"Not started")</f>
         <v/>
       </c>
       <c r="G9" s="31">
@@ -7736,7 +7829,7 @@
         <v/>
       </c>
       <c r="H9" s="32">
-        <f>SUMIFS('API Master List'!$K$2:$K$68,'API Master List'!$B$2:$B$68,"P4",'API Master List'!$F$2:$F$68,"Required")+SUMIFS('API Master List'!$K$2:$K$68,'API Master List'!$B$2:$B$68,"P4",'API Master List'!$F$2:$F$68,"Recommended")</f>
+        <f>SUMIFS('API Master List'!$K$2:$K$69,'API Master List'!$B$2:$B$69,"P4",'API Master List'!$F$2:$F$69,"Required")+SUMIFS('API Master List'!$K$2:$K$69,'API Master List'!$B$2:$B$69,"P4",'API Master List'!$F$2:$F$69,"Recommended")</f>
         <v/>
       </c>
     </row>
@@ -7837,7 +7930,7 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Anthropic key + $50 of credits. Generate CREDENTIALS_ENCRYPTION_KEY. Set spend caps in Settings → Control &amp; guardrails.</t>
+          <t>Groq API key (free tier is fine to start). Generate CREDENTIALS_ENCRYPTION_KEY. Set spend caps in Settings → Control &amp; guardrails.</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -8526,16 +8619,16 @@
       </c>
       <c r="B6" s="29" t="inlineStr">
         <is>
-          <t>Anthropic only</t>
+          <t>Groq only</t>
         </is>
       </c>
       <c r="C6" s="43">
-        <f>SUMIFS('API Master List'!$K$2:$K$68,'API Master List'!$B$2:$B$68,"P0")</f>
+        <f>SUMIFS('API Master List'!$K$2:$K$69,'API Master List'!$B$2:$B$69,"P0")</f>
         <v/>
       </c>
       <c r="D6" s="44" t="inlineStr">
         <is>
-          <t>≈$50 of credits goes a long way at this volume. Set a spend limit in the Anthropic console.</t>
+          <t>The free tier covers testing. Add billing before you schedule agents — the free rate limits will throttle 38 of them.</t>
         </is>
       </c>
     </row>
@@ -8547,11 +8640,11 @@
       </c>
       <c r="B7" s="29" t="inlineStr">
         <is>
-          <t>Anthropic, Apollo, verifier, Instantly, HubSpot, Stripe, GA4, Google Ads, Slack</t>
+          <t>Groq, Apollo, verifier, Instantly, HubSpot, Stripe, GA4, Google Ads, Slack</t>
         </is>
       </c>
       <c r="C7" s="43">
-        <f>SUMIFS('API Master List'!$K$2:$K$68,'API Master List'!$B$2:$B$68,"P0")+SUMIFS('API Master List'!$K$2:$K$68,'API Master List'!$B$2:$B$68,"P1",'API Master List'!$F$2:$F$68,"Required")+SUMIFS('API Master List'!$K$2:$K$68,'API Master List'!$B$2:$B$68,"P1",'API Master List'!$F$2:$F$68,"Recommended")</f>
+        <f>SUMIFS('API Master List'!$K$2:$K$69,'API Master List'!$B$2:$B$69,"P0")+SUMIFS('API Master List'!$K$2:$K$69,'API Master List'!$B$2:$B$69,"P1",'API Master List'!$F$2:$F$69,"Required")+SUMIFS('API Master List'!$K$2:$K$69,'API Master List'!$B$2:$B$69,"P1",'API Master List'!$F$2:$F$69,"Recommended")</f>
         <v/>
       </c>
       <c r="D7" s="44" t="inlineStr">
@@ -8572,7 +8665,7 @@
         </is>
       </c>
       <c r="C8" s="43">
-        <f>C7+SUMIFS('API Master List'!$K$2:$K$68,'API Master List'!$B$2:$B$68,"P2",'API Master List'!$F$2:$F$68,"Required")+SUMIFS('API Master List'!$K$2:$K$68,'API Master List'!$B$2:$B$68,"P2",'API Master List'!$F$2:$F$68,"Recommended")</f>
+        <f>C7+SUMIFS('API Master List'!$K$2:$K$69,'API Master List'!$B$2:$B$69,"P2",'API Master List'!$F$2:$F$69,"Required")+SUMIFS('API Master List'!$K$2:$K$69,'API Master List'!$B$2:$B$69,"P2",'API Master List'!$F$2:$F$69,"Recommended")</f>
         <v/>
       </c>
       <c r="D8" s="44" t="inlineStr">
@@ -8593,7 +8686,7 @@
         </is>
       </c>
       <c r="C9" s="43">
-        <f>C8+SUMIFS('API Master List'!$K$2:$K$68,'API Master List'!$B$2:$B$68,"P3",'API Master List'!$F$2:$F$68,"Required")+SUMIFS('API Master List'!$K$2:$K$68,'API Master List'!$B$2:$B$68,"P3",'API Master List'!$F$2:$F$68,"Recommended")+SUMIFS('API Master List'!$K$2:$K$68,'API Master List'!$B$2:$B$68,"P3",'API Master List'!$F$2:$F$68,"Optional")</f>
+        <f>C8+SUMIFS('API Master List'!$K$2:$K$69,'API Master List'!$B$2:$B$69,"P3",'API Master List'!$F$2:$F$69,"Required")+SUMIFS('API Master List'!$K$2:$K$69,'API Master List'!$B$2:$B$69,"P3",'API Master List'!$F$2:$F$69,"Recommended")+SUMIFS('API Master List'!$K$2:$K$69,'API Master List'!$B$2:$B$69,"P3",'API Master List'!$F$2:$F$69,"Optional")</f>
         <v/>
       </c>
       <c r="D9" s="44" t="inlineStr">
@@ -8614,7 +8707,7 @@
         </is>
       </c>
       <c r="C10" s="43">
-        <f>SUMIFS('API Master List'!$K$2:$K$68,'API Master List'!$F$2:$F$68,"Required")+SUMIFS('API Master List'!$K$2:$K$68,'API Master List'!$F$2:$F$68,"Recommended")+SUMIFS('API Master List'!$K$2:$K$68,'API Master List'!$F$2:$F$68,"Optional")</f>
+        <f>SUMIFS('API Master List'!$K$2:$K$69,'API Master List'!$F$2:$F$69,"Required")+SUMIFS('API Master List'!$K$2:$K$69,'API Master List'!$F$2:$F$69,"Recommended")+SUMIFS('API Master List'!$K$2:$K$69,'API Master List'!$F$2:$F$69,"Optional")</f>
         <v/>
       </c>
       <c r="D10" s="44" t="inlineStr">
@@ -8640,7 +8733,7 @@
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="46" t="inlineStr">
         <is>
-          <t>•  Claude usage scales with how often agents run. Start agents manually or daily, not hourly. Use the worker model (claude-sonnet-5) for bulk personalisation — it's already wired in ANTHROPIC_WORKER_MODEL.</t>
+          <t>•  LLM usage scales with how often agents run. Start agents manually or daily, not hourly. Bulk work (10k personalised emails, reply classification) already routes to the cheaper GROQ_WORKER_MODEL.</t>
         </is>
       </c>
     </row>
@@ -8693,7 +8786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E197"/>
+  <dimension ref="A1:E208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -9044,17 +9137,17 @@
     <row r="16">
       <c r="A16" s="44" t="inlineStr">
         <is>
-          <t>2. AI / LLM PROVIDERS  (the brain of every agent)</t>
+          <t>2. AI / LLM PROVIDER  (the brain of every agent)</t>
         </is>
       </c>
       <c r="B16" s="47" t="inlineStr">
         <is>
-          <t>ANTHROPIC_API_KEY</t>
+          <t>LLM_PROVIDER</t>
         </is>
       </c>
       <c r="C16" s="50" t="inlineStr">
         <is>
-          <t>Anthropic (Claude)</t>
+          <t>You choose: groq | anthropic | openai</t>
         </is>
       </c>
       <c r="D16" s="44" t="inlineStr">
@@ -9071,17 +9164,17 @@
     <row r="17">
       <c r="A17" s="44" t="inlineStr">
         <is>
-          <t>2. AI / LLM PROVIDERS  (the brain of every agent)</t>
+          <t>2. AI / LLM PROVIDER  (the brain of every agent)</t>
         </is>
       </c>
       <c r="B17" s="47" t="inlineStr">
         <is>
-          <t>ANTHROPIC_MODEL</t>
+          <t>GROQ_API_KEY</t>
         </is>
       </c>
       <c r="C17" s="50" t="inlineStr">
         <is>
-          <t>Anthropic (Claude)</t>
+          <t>Groq</t>
         </is>
       </c>
       <c r="D17" s="44" t="inlineStr">
@@ -9098,17 +9191,17 @@
     <row r="18">
       <c r="A18" s="44" t="inlineStr">
         <is>
-          <t>2. AI / LLM PROVIDERS  (the brain of every agent)</t>
+          <t>2. AI / LLM PROVIDER  (the brain of every agent)</t>
         </is>
       </c>
       <c r="B18" s="47" t="inlineStr">
         <is>
-          <t>ANTHROPIC_WORKER_MODEL</t>
+          <t>GROQ_MODEL</t>
         </is>
       </c>
       <c r="C18" s="50" t="inlineStr">
         <is>
-          <t>Anthropic (Claude)</t>
+          <t>Groq</t>
         </is>
       </c>
       <c r="D18" s="44" t="inlineStr">
@@ -9125,44 +9218,44 @@
     <row r="19">
       <c r="A19" s="44" t="inlineStr">
         <is>
-          <t>2. AI / LLM PROVIDERS  (the brain of every agent)</t>
+          <t>2. AI / LLM PROVIDER  (the brain of every agent)</t>
         </is>
       </c>
       <c r="B19" s="47" t="inlineStr">
         <is>
-          <t>ANTHROPIC_ENABLE_FALLBACKS</t>
-        </is>
-      </c>
-      <c r="C19" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>GROQ_WORKER_MODEL</t>
+        </is>
+      </c>
+      <c r="C19" s="50" t="inlineStr">
+        <is>
+          <t>Groq</t>
         </is>
       </c>
       <c r="D19" s="44" t="inlineStr">
         <is>
-          <t>Platform setting</t>
+          <t>Provider credential</t>
         </is>
       </c>
       <c r="E19" s="44" t="inlineStr">
         <is>
-          <t>Has a default</t>
+          <t>No — simulates if blank</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="44" t="inlineStr">
         <is>
-          <t>2. AI / LLM PROVIDERS  (the brain of every agent)</t>
+          <t>2. AI / LLM PROVIDER  (the brain of every agent)</t>
         </is>
       </c>
       <c r="B20" s="47" t="inlineStr">
         <is>
-          <t>OPENAI_API_KEY</t>
+          <t>GROQ_BASE_URL</t>
         </is>
       </c>
       <c r="C20" s="50" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Groq (tuning, leave blank)</t>
         </is>
       </c>
       <c r="D20" s="44" t="inlineStr">
@@ -9179,17 +9272,17 @@
     <row r="21">
       <c r="A21" s="44" t="inlineStr">
         <is>
-          <t>2. AI / LLM PROVIDERS  (the brain of every agent)</t>
+          <t>2. AI / LLM PROVIDER  (the brain of every agent)</t>
         </is>
       </c>
       <c r="B21" s="47" t="inlineStr">
         <is>
-          <t>GOOGLE_GEMINI_API_KEY</t>
+          <t>GROQ_TEMPERATURE</t>
         </is>
       </c>
       <c r="C21" s="50" t="inlineStr">
         <is>
-          <t>Google AI Studio (optional 2nd model)</t>
+          <t>Groq (tuning)</t>
         </is>
       </c>
       <c r="D21" s="44" t="inlineStr">
@@ -9206,17 +9299,17 @@
     <row r="22">
       <c r="A22" s="44" t="inlineStr">
         <is>
-          <t>2. AI / LLM PROVIDERS  (the brain of every agent)</t>
+          <t>2. AI / LLM PROVIDER  (the brain of every agent)</t>
         </is>
       </c>
       <c r="B22" s="47" t="inlineStr">
         <is>
-          <t>EMBEDDINGS_PROVIDER</t>
+          <t>GROQ_MAX_RETRIES</t>
         </is>
       </c>
       <c r="C22" s="50" t="inlineStr">
         <is>
-          <t>Voyage AI</t>
+          <t>Groq (tuning - raise on free tier)</t>
         </is>
       </c>
       <c r="D22" s="44" t="inlineStr">
@@ -9233,17 +9326,17 @@
     <row r="23">
       <c r="A23" s="44" t="inlineStr">
         <is>
-          <t>2. AI / LLM PROVIDERS  (the brain of every agent)</t>
+          <t>2. AI / LLM PROVIDER  (the brain of every agent)</t>
         </is>
       </c>
       <c r="B23" s="47" t="inlineStr">
         <is>
-          <t>VOYAGE_API_KEY</t>
+          <t>GROQ_TIMEOUT</t>
         </is>
       </c>
       <c r="C23" s="50" t="inlineStr">
         <is>
-          <t>Voyage AI</t>
+          <t>Groq (tuning)</t>
         </is>
       </c>
       <c r="D23" s="44" t="inlineStr">
@@ -9260,17 +9353,17 @@
     <row r="24">
       <c r="A24" s="44" t="inlineStr">
         <is>
-          <t>2. AI / LLM PROVIDERS  (the brain of every agent)</t>
+          <t>2. AI / LLM PROVIDER  (the brain of every agent)</t>
         </is>
       </c>
       <c r="B24" s="47" t="inlineStr">
         <is>
-          <t>PINECONE_API_KEY</t>
+          <t>GROQ_SEND_REASONING_EFFORT</t>
         </is>
       </c>
       <c r="C24" s="50" t="inlineStr">
         <is>
-          <t>Pinecone</t>
+          <t>Groq (tuning - model dependent)</t>
         </is>
       </c>
       <c r="D24" s="44" t="inlineStr">
@@ -9287,17 +9380,17 @@
     <row r="25">
       <c r="A25" s="44" t="inlineStr">
         <is>
-          <t>2. AI / LLM PROVIDERS  (the brain of every agent)</t>
+          <t>2. AI / LLM PROVIDER  (the brain of every agent)</t>
         </is>
       </c>
       <c r="B25" s="47" t="inlineStr">
         <is>
-          <t>PINECONE_INDEX</t>
+          <t>ANTHROPIC_API_KEY</t>
         </is>
       </c>
       <c r="C25" s="50" t="inlineStr">
         <is>
-          <t>Pinecone</t>
+          <t>Anthropic (Claude)</t>
         </is>
       </c>
       <c r="D25" s="44" t="inlineStr">
@@ -9314,17 +9407,17 @@
     <row r="26">
       <c r="A26" s="44" t="inlineStr">
         <is>
-          <t>2. AI / LLM PROVIDERS  (the brain of every agent)</t>
+          <t>2. AI / LLM PROVIDER  (the brain of every agent)</t>
         </is>
       </c>
       <c r="B26" s="47" t="inlineStr">
         <is>
-          <t>HIGGSFIELD_API_KEY</t>
+          <t>ANTHROPIC_MODEL</t>
         </is>
       </c>
       <c r="C26" s="50" t="inlineStr">
         <is>
-          <t>Higgsfield</t>
+          <t>Anthropic (Claude)</t>
         </is>
       </c>
       <c r="D26" s="44" t="inlineStr">
@@ -9341,17 +9434,17 @@
     <row r="27">
       <c r="A27" s="44" t="inlineStr">
         <is>
-          <t>2. AI / LLM PROVIDERS  (the brain of every agent)</t>
+          <t>2. AI / LLM PROVIDER  (the brain of every agent)</t>
         </is>
       </c>
       <c r="B27" s="47" t="inlineStr">
         <is>
-          <t>RUNWAY_API_KEY</t>
+          <t>ANTHROPIC_WORKER_MODEL</t>
         </is>
       </c>
       <c r="C27" s="50" t="inlineStr">
         <is>
-          <t>Runway</t>
+          <t>Anthropic (Claude)</t>
         </is>
       </c>
       <c r="D27" s="44" t="inlineStr">
@@ -9368,17 +9461,17 @@
     <row r="28">
       <c r="A28" s="44" t="inlineStr">
         <is>
-          <t>2. AI / LLM PROVIDERS  (the brain of every agent)</t>
+          <t>2. AI / LLM PROVIDER  (the brain of every agent)</t>
         </is>
       </c>
       <c r="B28" s="47" t="inlineStr">
         <is>
-          <t>ELEVENLABS_API_KEY</t>
+          <t>OPENAI_API_KEY</t>
         </is>
       </c>
       <c r="C28" s="50" t="inlineStr">
         <is>
-          <t>ElevenLabs</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D28" s="44" t="inlineStr">
@@ -9395,17 +9488,17 @@
     <row r="29">
       <c r="A29" s="44" t="inlineStr">
         <is>
-          <t>2. AI / LLM PROVIDERS  (the brain of every agent)</t>
+          <t>2. AI / LLM PROVIDER  (the brain of every agent)</t>
         </is>
       </c>
       <c r="B29" s="47" t="inlineStr">
         <is>
-          <t>STABILITY_API_KEY</t>
+          <t>OPENAI_MODEL</t>
         </is>
       </c>
       <c r="C29" s="50" t="inlineStr">
         <is>
-          <t>Stability AI</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D29" s="44" t="inlineStr">
@@ -9422,17 +9515,17 @@
     <row r="30">
       <c r="A30" s="44" t="inlineStr">
         <is>
-          <t>2. AI / LLM PROVIDERS  (the brain of every agent)</t>
+          <t>2. AI / LLM PROVIDER  (the brain of every agent)</t>
         </is>
       </c>
       <c r="B30" s="47" t="inlineStr">
         <is>
-          <t>FAL_API_KEY</t>
+          <t>OPENAI_WORKER_MODEL</t>
         </is>
       </c>
       <c r="C30" s="50" t="inlineStr">
         <is>
-          <t>fal.ai</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="D30" s="44" t="inlineStr">
@@ -9449,17 +9542,17 @@
     <row r="31">
       <c r="A31" s="44" t="inlineStr">
         <is>
-          <t>3. PAID MEDIA  (Paid Media Agent + Autonomous Media Buyer)</t>
+          <t>2. AI / LLM PROVIDER  (the brain of every agent)</t>
         </is>
       </c>
       <c r="B31" s="47" t="inlineStr">
         <is>
-          <t>META_APP_ID</t>
+          <t>OPENAI_BASE_URL</t>
         </is>
       </c>
       <c r="C31" s="50" t="inlineStr">
         <is>
-          <t>Meta Ads (Facebook + Instagram)</t>
+          <t>OpenAI-compatible gateway (optional)</t>
         </is>
       </c>
       <c r="D31" s="44" t="inlineStr">
@@ -9476,17 +9569,17 @@
     <row r="32">
       <c r="A32" s="44" t="inlineStr">
         <is>
-          <t>3. PAID MEDIA  (Paid Media Agent + Autonomous Media Buyer)</t>
+          <t>2. AI / LLM PROVIDER  (the brain of every agent)</t>
         </is>
       </c>
       <c r="B32" s="47" t="inlineStr">
         <is>
-          <t>META_APP_SECRET</t>
+          <t>GOOGLE_GEMINI_API_KEY</t>
         </is>
       </c>
       <c r="C32" s="50" t="inlineStr">
         <is>
-          <t>Meta Ads (Facebook + Instagram)</t>
+          <t>Google AI Studio (optional 2nd model)</t>
         </is>
       </c>
       <c r="D32" s="44" t="inlineStr">
@@ -9503,17 +9596,17 @@
     <row r="33">
       <c r="A33" s="44" t="inlineStr">
         <is>
-          <t>3. PAID MEDIA  (Paid Media Agent + Autonomous Media Buyer)</t>
+          <t>2. AI / LLM PROVIDER  (the brain of every agent)</t>
         </is>
       </c>
       <c r="B33" s="47" t="inlineStr">
         <is>
-          <t>META_ACCESS_TOKEN</t>
+          <t>EMBEDDINGS_PROVIDER</t>
         </is>
       </c>
       <c r="C33" s="50" t="inlineStr">
         <is>
-          <t>Meta Ads (Facebook + Instagram)</t>
+          <t>Voyage AI</t>
         </is>
       </c>
       <c r="D33" s="44" t="inlineStr">
@@ -9530,17 +9623,17 @@
     <row r="34">
       <c r="A34" s="44" t="inlineStr">
         <is>
-          <t>3. PAID MEDIA  (Paid Media Agent + Autonomous Media Buyer)</t>
+          <t>2. AI / LLM PROVIDER  (the brain of every agent)</t>
         </is>
       </c>
       <c r="B34" s="47" t="inlineStr">
         <is>
-          <t>META_AD_ACCOUNT_ID</t>
+          <t>VOYAGE_API_KEY</t>
         </is>
       </c>
       <c r="C34" s="50" t="inlineStr">
         <is>
-          <t>Meta Ads (Facebook + Instagram)</t>
+          <t>Voyage AI</t>
         </is>
       </c>
       <c r="D34" s="44" t="inlineStr">
@@ -9557,17 +9650,17 @@
     <row r="35">
       <c r="A35" s="44" t="inlineStr">
         <is>
-          <t>3. PAID MEDIA  (Paid Media Agent + Autonomous Media Buyer)</t>
+          <t>2. AI / LLM PROVIDER  (the brain of every agent)</t>
         </is>
       </c>
       <c r="B35" s="47" t="inlineStr">
         <is>
-          <t>META_PIXEL_ID</t>
+          <t>PINECONE_API_KEY</t>
         </is>
       </c>
       <c r="C35" s="50" t="inlineStr">
         <is>
-          <t>Meta Ads (Facebook + Instagram)</t>
+          <t>Pinecone</t>
         </is>
       </c>
       <c r="D35" s="44" t="inlineStr">
@@ -9584,17 +9677,17 @@
     <row r="36">
       <c r="A36" s="44" t="inlineStr">
         <is>
-          <t>3. PAID MEDIA  (Paid Media Agent + Autonomous Media Buyer)</t>
+          <t>2. AI / LLM PROVIDER  (the brain of every agent)</t>
         </is>
       </c>
       <c r="B36" s="47" t="inlineStr">
         <is>
-          <t>META_PAGE_ID</t>
+          <t>PINECONE_INDEX</t>
         </is>
       </c>
       <c r="C36" s="50" t="inlineStr">
         <is>
-          <t>Meta Ads (Facebook + Instagram)</t>
+          <t>Pinecone</t>
         </is>
       </c>
       <c r="D36" s="44" t="inlineStr">
@@ -9611,17 +9704,17 @@
     <row r="37">
       <c r="A37" s="44" t="inlineStr">
         <is>
-          <t>3. PAID MEDIA  (Paid Media Agent + Autonomous Media Buyer)</t>
+          <t>2. AI / LLM PROVIDER  (the brain of every agent)</t>
         </is>
       </c>
       <c r="B37" s="47" t="inlineStr">
         <is>
-          <t>META_INSTAGRAM_ACCOUNT_ID</t>
+          <t>HIGGSFIELD_API_KEY</t>
         </is>
       </c>
       <c r="C37" s="50" t="inlineStr">
         <is>
-          <t>Meta Ads (Facebook + Instagram)</t>
+          <t>Higgsfield</t>
         </is>
       </c>
       <c r="D37" s="44" t="inlineStr">
@@ -9638,17 +9731,17 @@
     <row r="38">
       <c r="A38" s="44" t="inlineStr">
         <is>
-          <t>3. PAID MEDIA  (Paid Media Agent + Autonomous Media Buyer)</t>
+          <t>2. AI / LLM PROVIDER  (the brain of every agent)</t>
         </is>
       </c>
       <c r="B38" s="47" t="inlineStr">
         <is>
-          <t>META_API_VERSION</t>
+          <t>RUNWAY_API_KEY</t>
         </is>
       </c>
       <c r="C38" s="50" t="inlineStr">
         <is>
-          <t>Meta Ads (Facebook + Instagram)</t>
+          <t>Runway</t>
         </is>
       </c>
       <c r="D38" s="44" t="inlineStr">
@@ -9665,17 +9758,17 @@
     <row r="39">
       <c r="A39" s="44" t="inlineStr">
         <is>
-          <t>3. PAID MEDIA  (Paid Media Agent + Autonomous Media Buyer)</t>
+          <t>2. AI / LLM PROVIDER  (the brain of every agent)</t>
         </is>
       </c>
       <c r="B39" s="47" t="inlineStr">
         <is>
-          <t>META_WEBHOOK_VERIFY_TOKEN</t>
+          <t>ELEVENLABS_API_KEY</t>
         </is>
       </c>
       <c r="C39" s="50" t="inlineStr">
         <is>
-          <t>You invent this string (must match Meta)</t>
+          <t>ElevenLabs</t>
         </is>
       </c>
       <c r="D39" s="44" t="inlineStr">
@@ -9692,17 +9785,17 @@
     <row r="40">
       <c r="A40" s="44" t="inlineStr">
         <is>
-          <t>3. PAID MEDIA  (Paid Media Agent + Autonomous Media Buyer)</t>
+          <t>2. AI / LLM PROVIDER  (the brain of every agent)</t>
         </is>
       </c>
       <c r="B40" s="47" t="inlineStr">
         <is>
-          <t>GOOGLE_ADS_DEVELOPER_TOKEN</t>
+          <t>STABILITY_API_KEY</t>
         </is>
       </c>
       <c r="C40" s="50" t="inlineStr">
         <is>
-          <t>Google Ads</t>
+          <t>Stability AI</t>
         </is>
       </c>
       <c r="D40" s="44" t="inlineStr">
@@ -9719,17 +9812,17 @@
     <row r="41">
       <c r="A41" s="44" t="inlineStr">
         <is>
-          <t>3. PAID MEDIA  (Paid Media Agent + Autonomous Media Buyer)</t>
+          <t>2. AI / LLM PROVIDER  (the brain of every agent)</t>
         </is>
       </c>
       <c r="B41" s="47" t="inlineStr">
         <is>
-          <t>GOOGLE_ADS_CLIENT_ID</t>
+          <t>FAL_API_KEY</t>
         </is>
       </c>
       <c r="C41" s="50" t="inlineStr">
         <is>
-          <t>Google Ads</t>
+          <t>fal.ai</t>
         </is>
       </c>
       <c r="D41" s="44" t="inlineStr">
@@ -9751,12 +9844,12 @@
       </c>
       <c r="B42" s="47" t="inlineStr">
         <is>
-          <t>GOOGLE_ADS_CLIENT_SECRET</t>
+          <t>META_APP_ID</t>
         </is>
       </c>
       <c r="C42" s="50" t="inlineStr">
         <is>
-          <t>Google Ads</t>
+          <t>Meta Ads (Facebook + Instagram)</t>
         </is>
       </c>
       <c r="D42" s="44" t="inlineStr">
@@ -9778,12 +9871,12 @@
       </c>
       <c r="B43" s="47" t="inlineStr">
         <is>
-          <t>GOOGLE_ADS_REFRESH_TOKEN</t>
+          <t>META_APP_SECRET</t>
         </is>
       </c>
       <c r="C43" s="50" t="inlineStr">
         <is>
-          <t>Google Ads</t>
+          <t>Meta Ads (Facebook + Instagram)</t>
         </is>
       </c>
       <c r="D43" s="44" t="inlineStr">
@@ -9805,12 +9898,12 @@
       </c>
       <c r="B44" s="47" t="inlineStr">
         <is>
-          <t>GOOGLE_ADS_LOGIN_CUSTOMER_ID</t>
+          <t>META_ACCESS_TOKEN</t>
         </is>
       </c>
       <c r="C44" s="50" t="inlineStr">
         <is>
-          <t>Google Ads</t>
+          <t>Meta Ads (Facebook + Instagram)</t>
         </is>
       </c>
       <c r="D44" s="44" t="inlineStr">
@@ -9832,12 +9925,12 @@
       </c>
       <c r="B45" s="47" t="inlineStr">
         <is>
-          <t>GOOGLE_ADS_CUSTOMER_ID</t>
+          <t>META_AD_ACCOUNT_ID</t>
         </is>
       </c>
       <c r="C45" s="50" t="inlineStr">
         <is>
-          <t>Google Ads</t>
+          <t>Meta Ads (Facebook + Instagram)</t>
         </is>
       </c>
       <c r="D45" s="44" t="inlineStr">
@@ -9859,12 +9952,12 @@
       </c>
       <c r="B46" s="47" t="inlineStr">
         <is>
-          <t>LINKEDIN_CLIENT_ID</t>
+          <t>META_PIXEL_ID</t>
         </is>
       </c>
       <c r="C46" s="50" t="inlineStr">
         <is>
-          <t>LinkedIn Marketing API</t>
+          <t>Meta Ads (Facebook + Instagram)</t>
         </is>
       </c>
       <c r="D46" s="44" t="inlineStr">
@@ -9886,12 +9979,12 @@
       </c>
       <c r="B47" s="47" t="inlineStr">
         <is>
-          <t>LINKEDIN_CLIENT_SECRET</t>
+          <t>META_PAGE_ID</t>
         </is>
       </c>
       <c r="C47" s="50" t="inlineStr">
         <is>
-          <t>LinkedIn Marketing API</t>
+          <t>Meta Ads (Facebook + Instagram)</t>
         </is>
       </c>
       <c r="D47" s="44" t="inlineStr">
@@ -9913,12 +10006,12 @@
       </c>
       <c r="B48" s="47" t="inlineStr">
         <is>
-          <t>LINKEDIN_ACCESS_TOKEN</t>
+          <t>META_INSTAGRAM_ACCOUNT_ID</t>
         </is>
       </c>
       <c r="C48" s="50" t="inlineStr">
         <is>
-          <t>LinkedIn Marketing API</t>
+          <t>Meta Ads (Facebook + Instagram)</t>
         </is>
       </c>
       <c r="D48" s="44" t="inlineStr">
@@ -9940,12 +10033,12 @@
       </c>
       <c r="B49" s="47" t="inlineStr">
         <is>
-          <t>LINKEDIN_AD_ACCOUNT_ID</t>
+          <t>META_API_VERSION</t>
         </is>
       </c>
       <c r="C49" s="50" t="inlineStr">
         <is>
-          <t>LinkedIn Marketing API</t>
+          <t>Meta Ads (Facebook + Instagram)</t>
         </is>
       </c>
       <c r="D49" s="44" t="inlineStr">
@@ -9967,12 +10060,12 @@
       </c>
       <c r="B50" s="47" t="inlineStr">
         <is>
-          <t>LINKEDIN_ORGANIZATION_ID</t>
+          <t>META_WEBHOOK_VERIFY_TOKEN</t>
         </is>
       </c>
       <c r="C50" s="50" t="inlineStr">
         <is>
-          <t>LinkedIn Marketing API</t>
+          <t>You invent this string (must match Meta)</t>
         </is>
       </c>
       <c r="D50" s="44" t="inlineStr">
@@ -9994,12 +10087,12 @@
       </c>
       <c r="B51" s="47" t="inlineStr">
         <is>
-          <t>TIKTOK_APP_ID</t>
+          <t>GOOGLE_ADS_DEVELOPER_TOKEN</t>
         </is>
       </c>
       <c r="C51" s="50" t="inlineStr">
         <is>
-          <t>TikTok Ads</t>
+          <t>Google Ads</t>
         </is>
       </c>
       <c r="D51" s="44" t="inlineStr">
@@ -10021,12 +10114,12 @@
       </c>
       <c r="B52" s="47" t="inlineStr">
         <is>
-          <t>TIKTOK_APP_SECRET</t>
+          <t>GOOGLE_ADS_CLIENT_ID</t>
         </is>
       </c>
       <c r="C52" s="50" t="inlineStr">
         <is>
-          <t>TikTok Ads</t>
+          <t>Google Ads</t>
         </is>
       </c>
       <c r="D52" s="44" t="inlineStr">
@@ -10048,12 +10141,12 @@
       </c>
       <c r="B53" s="47" t="inlineStr">
         <is>
-          <t>TIKTOK_ACCESS_TOKEN</t>
+          <t>GOOGLE_ADS_CLIENT_SECRET</t>
         </is>
       </c>
       <c r="C53" s="50" t="inlineStr">
         <is>
-          <t>TikTok Ads</t>
+          <t>Google Ads</t>
         </is>
       </c>
       <c r="D53" s="44" t="inlineStr">
@@ -10075,12 +10168,12 @@
       </c>
       <c r="B54" s="47" t="inlineStr">
         <is>
-          <t>TIKTOK_ADVERTISER_ID</t>
+          <t>GOOGLE_ADS_REFRESH_TOKEN</t>
         </is>
       </c>
       <c r="C54" s="50" t="inlineStr">
         <is>
-          <t>TikTok Ads</t>
+          <t>Google Ads</t>
         </is>
       </c>
       <c r="D54" s="44" t="inlineStr">
@@ -10102,12 +10195,12 @@
       </c>
       <c r="B55" s="47" t="inlineStr">
         <is>
-          <t>X_API_KEY</t>
+          <t>GOOGLE_ADS_LOGIN_CUSTOMER_ID</t>
         </is>
       </c>
       <c r="C55" s="50" t="inlineStr">
         <is>
-          <t>X (Twitter) Ads</t>
+          <t>Google Ads</t>
         </is>
       </c>
       <c r="D55" s="44" t="inlineStr">
@@ -10129,12 +10222,12 @@
       </c>
       <c r="B56" s="47" t="inlineStr">
         <is>
-          <t>X_API_SECRET</t>
+          <t>GOOGLE_ADS_CUSTOMER_ID</t>
         </is>
       </c>
       <c r="C56" s="50" t="inlineStr">
         <is>
-          <t>X (Twitter) Ads</t>
+          <t>Google Ads</t>
         </is>
       </c>
       <c r="D56" s="44" t="inlineStr">
@@ -10156,12 +10249,12 @@
       </c>
       <c r="B57" s="47" t="inlineStr">
         <is>
-          <t>X_ACCESS_TOKEN</t>
+          <t>LINKEDIN_CLIENT_ID</t>
         </is>
       </c>
       <c r="C57" s="50" t="inlineStr">
         <is>
-          <t>X (Twitter) Ads</t>
+          <t>LinkedIn Marketing API</t>
         </is>
       </c>
       <c r="D57" s="44" t="inlineStr">
@@ -10183,12 +10276,12 @@
       </c>
       <c r="B58" s="47" t="inlineStr">
         <is>
-          <t>X_ACCESS_TOKEN_SECRET</t>
+          <t>LINKEDIN_CLIENT_SECRET</t>
         </is>
       </c>
       <c r="C58" s="50" t="inlineStr">
         <is>
-          <t>X (Twitter) Ads</t>
+          <t>LinkedIn Marketing API</t>
         </is>
       </c>
       <c r="D58" s="44" t="inlineStr">
@@ -10210,12 +10303,12 @@
       </c>
       <c r="B59" s="47" t="inlineStr">
         <is>
-          <t>X_ADS_ACCOUNT_ID</t>
+          <t>LINKEDIN_ACCESS_TOKEN</t>
         </is>
       </c>
       <c r="C59" s="50" t="inlineStr">
         <is>
-          <t>X (Twitter) Ads</t>
+          <t>LinkedIn Marketing API</t>
         </is>
       </c>
       <c r="D59" s="44" t="inlineStr">
@@ -10232,17 +10325,17 @@
     <row r="60">
       <c r="A60" s="44" t="inlineStr">
         <is>
-          <t>4. ORGANIC SOCIAL  (Social Media Agent + LinkedIn Agent)</t>
+          <t>3. PAID MEDIA  (Paid Media Agent + Autonomous Media Buyer)</t>
         </is>
       </c>
       <c r="B60" s="47" t="inlineStr">
         <is>
-          <t>YOUTUBE_CLIENT_ID</t>
+          <t>LINKEDIN_AD_ACCOUNT_ID</t>
         </is>
       </c>
       <c r="C60" s="50" t="inlineStr">
         <is>
-          <t>YouTube Data API</t>
+          <t>LinkedIn Marketing API</t>
         </is>
       </c>
       <c r="D60" s="44" t="inlineStr">
@@ -10259,17 +10352,17 @@
     <row r="61">
       <c r="A61" s="44" t="inlineStr">
         <is>
-          <t>4. ORGANIC SOCIAL  (Social Media Agent + LinkedIn Agent)</t>
+          <t>3. PAID MEDIA  (Paid Media Agent + Autonomous Media Buyer)</t>
         </is>
       </c>
       <c r="B61" s="47" t="inlineStr">
         <is>
-          <t>YOUTUBE_CLIENT_SECRET</t>
+          <t>LINKEDIN_ORGANIZATION_ID</t>
         </is>
       </c>
       <c r="C61" s="50" t="inlineStr">
         <is>
-          <t>YouTube Data API</t>
+          <t>LinkedIn Marketing API</t>
         </is>
       </c>
       <c r="D61" s="44" t="inlineStr">
@@ -10286,17 +10379,17 @@
     <row r="62">
       <c r="A62" s="44" t="inlineStr">
         <is>
-          <t>4. ORGANIC SOCIAL  (Social Media Agent + LinkedIn Agent)</t>
+          <t>3. PAID MEDIA  (Paid Media Agent + Autonomous Media Buyer)</t>
         </is>
       </c>
       <c r="B62" s="47" t="inlineStr">
         <is>
-          <t>YOUTUBE_REFRESH_TOKEN</t>
+          <t>TIKTOK_APP_ID</t>
         </is>
       </c>
       <c r="C62" s="50" t="inlineStr">
         <is>
-          <t>YouTube Data API</t>
+          <t>TikTok Ads</t>
         </is>
       </c>
       <c r="D62" s="44" t="inlineStr">
@@ -10313,17 +10406,17 @@
     <row r="63">
       <c r="A63" s="44" t="inlineStr">
         <is>
-          <t>4. ORGANIC SOCIAL  (Social Media Agent + LinkedIn Agent)</t>
+          <t>3. PAID MEDIA  (Paid Media Agent + Autonomous Media Buyer)</t>
         </is>
       </c>
       <c r="B63" s="47" t="inlineStr">
         <is>
-          <t>YOUTUBE_CHANNEL_ID</t>
+          <t>TIKTOK_APP_SECRET</t>
         </is>
       </c>
       <c r="C63" s="50" t="inlineStr">
         <is>
-          <t>YouTube Data API</t>
+          <t>TikTok Ads</t>
         </is>
       </c>
       <c r="D63" s="44" t="inlineStr">
@@ -10340,17 +10433,17 @@
     <row r="64">
       <c r="A64" s="44" t="inlineStr">
         <is>
-          <t>4. ORGANIC SOCIAL  (Social Media Agent + LinkedIn Agent)</t>
+          <t>3. PAID MEDIA  (Paid Media Agent + Autonomous Media Buyer)</t>
         </is>
       </c>
       <c r="B64" s="47" t="inlineStr">
         <is>
-          <t>TIKTOK_CONTENT_CLIENT_KEY</t>
+          <t>TIKTOK_ACCESS_TOKEN</t>
         </is>
       </c>
       <c r="C64" s="50" t="inlineStr">
         <is>
-          <t>TikTok Content Posting</t>
+          <t>TikTok Ads</t>
         </is>
       </c>
       <c r="D64" s="44" t="inlineStr">
@@ -10367,17 +10460,17 @@
     <row r="65">
       <c r="A65" s="44" t="inlineStr">
         <is>
-          <t>4. ORGANIC SOCIAL  (Social Media Agent + LinkedIn Agent)</t>
+          <t>3. PAID MEDIA  (Paid Media Agent + Autonomous Media Buyer)</t>
         </is>
       </c>
       <c r="B65" s="47" t="inlineStr">
         <is>
-          <t>TIKTOK_CONTENT_CLIENT_SECRET</t>
+          <t>TIKTOK_ADVERTISER_ID</t>
         </is>
       </c>
       <c r="C65" s="50" t="inlineStr">
         <is>
-          <t>TikTok Content Posting</t>
+          <t>TikTok Ads</t>
         </is>
       </c>
       <c r="D65" s="44" t="inlineStr">
@@ -10394,17 +10487,17 @@
     <row r="66">
       <c r="A66" s="44" t="inlineStr">
         <is>
-          <t>4. ORGANIC SOCIAL  (Social Media Agent + LinkedIn Agent)</t>
+          <t>3. PAID MEDIA  (Paid Media Agent + Autonomous Media Buyer)</t>
         </is>
       </c>
       <c r="B66" s="47" t="inlineStr">
         <is>
-          <t>BUFFER_ACCESS_TOKEN</t>
+          <t>X_API_KEY</t>
         </is>
       </c>
       <c r="C66" s="50" t="inlineStr">
         <is>
-          <t>Buffer (alternative to Ayrshare)</t>
+          <t>X (Twitter) Ads</t>
         </is>
       </c>
       <c r="D66" s="44" t="inlineStr">
@@ -10421,17 +10514,17 @@
     <row r="67">
       <c r="A67" s="44" t="inlineStr">
         <is>
-          <t>4. ORGANIC SOCIAL  (Social Media Agent + LinkedIn Agent)</t>
+          <t>3. PAID MEDIA  (Paid Media Agent + Autonomous Media Buyer)</t>
         </is>
       </c>
       <c r="B67" s="47" t="inlineStr">
         <is>
-          <t>AYRSHARE_API_KEY</t>
+          <t>X_API_SECRET</t>
         </is>
       </c>
       <c r="C67" s="50" t="inlineStr">
         <is>
-          <t>Ayrshare</t>
+          <t>X (Twitter) Ads</t>
         </is>
       </c>
       <c r="D67" s="44" t="inlineStr">
@@ -10448,17 +10541,17 @@
     <row r="68">
       <c r="A68" s="44" t="inlineStr">
         <is>
-          <t>5. PROSPECTING &amp; DATA ENRICHMENT  (waterfall order = priority order)</t>
+          <t>3. PAID MEDIA  (Paid Media Agent + Autonomous Media Buyer)</t>
         </is>
       </c>
       <c r="B68" s="47" t="inlineStr">
         <is>
-          <t>ENRICHMENT_WATERFALL</t>
+          <t>X_ACCESS_TOKEN</t>
         </is>
       </c>
       <c r="C68" s="50" t="inlineStr">
         <is>
-          <t>Hunter.io</t>
+          <t>X (Twitter) Ads</t>
         </is>
       </c>
       <c r="D68" s="44" t="inlineStr">
@@ -10475,17 +10568,17 @@
     <row r="69">
       <c r="A69" s="44" t="inlineStr">
         <is>
-          <t>5. PROSPECTING &amp; DATA ENRICHMENT  (waterfall order = priority order)</t>
+          <t>3. PAID MEDIA  (Paid Media Agent + Autonomous Media Buyer)</t>
         </is>
       </c>
       <c r="B69" s="47" t="inlineStr">
         <is>
-          <t>APOLLO_API_KEY</t>
+          <t>X_ACCESS_TOKEN_SECRET</t>
         </is>
       </c>
       <c r="C69" s="50" t="inlineStr">
         <is>
-          <t>Apollo.io</t>
+          <t>X (Twitter) Ads</t>
         </is>
       </c>
       <c r="D69" s="44" t="inlineStr">
@@ -10502,17 +10595,17 @@
     <row r="70">
       <c r="A70" s="44" t="inlineStr">
         <is>
-          <t>5. PROSPECTING &amp; DATA ENRICHMENT  (waterfall order = priority order)</t>
+          <t>3. PAID MEDIA  (Paid Media Agent + Autonomous Media Buyer)</t>
         </is>
       </c>
       <c r="B70" s="47" t="inlineStr">
         <is>
-          <t>CLEARBIT_API_KEY</t>
+          <t>X_ADS_ACCOUNT_ID</t>
         </is>
       </c>
       <c r="C70" s="50" t="inlineStr">
         <is>
-          <t>Clearbit (HubSpot Breeze Intelligence)</t>
+          <t>X (Twitter) Ads</t>
         </is>
       </c>
       <c r="D70" s="44" t="inlineStr">
@@ -10529,17 +10622,17 @@
     <row r="71">
       <c r="A71" s="44" t="inlineStr">
         <is>
-          <t>5. PROSPECTING &amp; DATA ENRICHMENT  (waterfall order = priority order)</t>
+          <t>4. ORGANIC SOCIAL  (Social Media Agent + LinkedIn Agent)</t>
         </is>
       </c>
       <c r="B71" s="47" t="inlineStr">
         <is>
-          <t>PEOPLE_DATA_LABS_API_KEY</t>
+          <t>YOUTUBE_CLIENT_ID</t>
         </is>
       </c>
       <c r="C71" s="50" t="inlineStr">
         <is>
-          <t>People Data Labs</t>
+          <t>YouTube Data API</t>
         </is>
       </c>
       <c r="D71" s="44" t="inlineStr">
@@ -10556,17 +10649,17 @@
     <row r="72">
       <c r="A72" s="44" t="inlineStr">
         <is>
-          <t>5. PROSPECTING &amp; DATA ENRICHMENT  (waterfall order = priority order)</t>
+          <t>4. ORGANIC SOCIAL  (Social Media Agent + LinkedIn Agent)</t>
         </is>
       </c>
       <c r="B72" s="47" t="inlineStr">
         <is>
-          <t>HUNTER_API_KEY</t>
+          <t>YOUTUBE_CLIENT_SECRET</t>
         </is>
       </c>
       <c r="C72" s="50" t="inlineStr">
         <is>
-          <t>Hunter.io</t>
+          <t>YouTube Data API</t>
         </is>
       </c>
       <c r="D72" s="44" t="inlineStr">
@@ -10583,17 +10676,17 @@
     <row r="73">
       <c r="A73" s="44" t="inlineStr">
         <is>
-          <t>5. PROSPECTING &amp; DATA ENRICHMENT  (waterfall order = priority order)</t>
+          <t>4. ORGANIC SOCIAL  (Social Media Agent + LinkedIn Agent)</t>
         </is>
       </c>
       <c r="B73" s="47" t="inlineStr">
         <is>
-          <t>ZOOMINFO_USERNAME</t>
+          <t>YOUTUBE_REFRESH_TOKEN</t>
         </is>
       </c>
       <c r="C73" s="50" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>YouTube Data API</t>
         </is>
       </c>
       <c r="D73" s="44" t="inlineStr">
@@ -10610,17 +10703,17 @@
     <row r="74">
       <c r="A74" s="44" t="inlineStr">
         <is>
-          <t>5. PROSPECTING &amp; DATA ENRICHMENT  (waterfall order = priority order)</t>
+          <t>4. ORGANIC SOCIAL  (Social Media Agent + LinkedIn Agent)</t>
         </is>
       </c>
       <c r="B74" s="47" t="inlineStr">
         <is>
-          <t>ZOOMINFO_PASSWORD</t>
+          <t>YOUTUBE_CHANNEL_ID</t>
         </is>
       </c>
       <c r="C74" s="50" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>YouTube Data API</t>
         </is>
       </c>
       <c r="D74" s="44" t="inlineStr">
@@ -10637,17 +10730,17 @@
     <row r="75">
       <c r="A75" s="44" t="inlineStr">
         <is>
-          <t>5. PROSPECTING &amp; DATA ENRICHMENT  (waterfall order = priority order)</t>
+          <t>4. ORGANIC SOCIAL  (Social Media Agent + LinkedIn Agent)</t>
         </is>
       </c>
       <c r="B75" s="47" t="inlineStr">
         <is>
-          <t>ZOOMINFO_CLIENT_ID</t>
+          <t>TIKTOK_CONTENT_CLIENT_KEY</t>
         </is>
       </c>
       <c r="C75" s="50" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>TikTok Content Posting</t>
         </is>
       </c>
       <c r="D75" s="44" t="inlineStr">
@@ -10664,17 +10757,17 @@
     <row r="76">
       <c r="A76" s="44" t="inlineStr">
         <is>
-          <t>5. PROSPECTING &amp; DATA ENRICHMENT  (waterfall order = priority order)</t>
+          <t>4. ORGANIC SOCIAL  (Social Media Agent + LinkedIn Agent)</t>
         </is>
       </c>
       <c r="B76" s="47" t="inlineStr">
         <is>
-          <t>ZOOMINFO_PRIVATE_KEY</t>
+          <t>TIKTOK_CONTENT_CLIENT_SECRET</t>
         </is>
       </c>
       <c r="C76" s="50" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>TikTok Content Posting</t>
         </is>
       </c>
       <c r="D76" s="44" t="inlineStr">
@@ -10691,17 +10784,17 @@
     <row r="77">
       <c r="A77" s="44" t="inlineStr">
         <is>
-          <t>5. PROSPECTING &amp; DATA ENRICHMENT  (waterfall order = priority order)</t>
+          <t>4. ORGANIC SOCIAL  (Social Media Agent + LinkedIn Agent)</t>
         </is>
       </c>
       <c r="B77" s="47" t="inlineStr">
         <is>
-          <t>LUSHA_API_KEY</t>
+          <t>BUFFER_ACCESS_TOKEN</t>
         </is>
       </c>
       <c r="C77" s="50" t="inlineStr">
         <is>
-          <t>Lusha (alternative enrichment)</t>
+          <t>Buffer (alternative to Ayrshare)</t>
         </is>
       </c>
       <c r="D77" s="44" t="inlineStr">
@@ -10718,17 +10811,17 @@
     <row r="78">
       <c r="A78" s="44" t="inlineStr">
         <is>
-          <t>5. PROSPECTING &amp; DATA ENRICHMENT  (waterfall order = priority order)</t>
+          <t>4. ORGANIC SOCIAL  (Social Media Agent + LinkedIn Agent)</t>
         </is>
       </c>
       <c r="B78" s="47" t="inlineStr">
         <is>
-          <t>CRUNCHBASE_API_KEY</t>
+          <t>AYRSHARE_API_KEY</t>
         </is>
       </c>
       <c r="C78" s="50" t="inlineStr">
         <is>
-          <t>Crunchbase</t>
+          <t>Ayrshare</t>
         </is>
       </c>
       <c r="D78" s="44" t="inlineStr">
@@ -10750,12 +10843,12 @@
       </c>
       <c r="B79" s="47" t="inlineStr">
         <is>
-          <t>BUILTWITH_API_KEY</t>
+          <t>ENRICHMENT_WATERFALL</t>
         </is>
       </c>
       <c r="C79" s="50" t="inlineStr">
         <is>
-          <t>BuiltWith</t>
+          <t>Hunter.io</t>
         </is>
       </c>
       <c r="D79" s="44" t="inlineStr">
@@ -10777,12 +10870,12 @@
       </c>
       <c r="B80" s="47" t="inlineStr">
         <is>
-          <t>PROXYCURL_API_KEY</t>
+          <t>APOLLO_API_KEY</t>
         </is>
       </c>
       <c r="C80" s="50" t="inlineStr">
         <is>
-          <t>Proxycurl</t>
+          <t>Apollo.io</t>
         </is>
       </c>
       <c r="D80" s="44" t="inlineStr">
@@ -10804,12 +10897,12 @@
       </c>
       <c r="B81" s="47" t="inlineStr">
         <is>
-          <t>EMAIL_VERIFICATION_WATERFALL</t>
+          <t>CLEARBIT_API_KEY</t>
         </is>
       </c>
       <c r="C81" s="50" t="inlineStr">
         <is>
-          <t>MillionVerifier</t>
+          <t>Clearbit (HubSpot Breeze Intelligence)</t>
         </is>
       </c>
       <c r="D81" s="44" t="inlineStr">
@@ -10831,12 +10924,12 @@
       </c>
       <c r="B82" s="47" t="inlineStr">
         <is>
-          <t>ZEROBOUNCE_API_KEY</t>
+          <t>PEOPLE_DATA_LABS_API_KEY</t>
         </is>
       </c>
       <c r="C82" s="50" t="inlineStr">
         <is>
-          <t>ZeroBounce</t>
+          <t>People Data Labs</t>
         </is>
       </c>
       <c r="D82" s="44" t="inlineStr">
@@ -10858,12 +10951,12 @@
       </c>
       <c r="B83" s="47" t="inlineStr">
         <is>
-          <t>NEVERBOUNCE_API_KEY</t>
+          <t>HUNTER_API_KEY</t>
         </is>
       </c>
       <c r="C83" s="50" t="inlineStr">
         <is>
-          <t>NeverBounce</t>
+          <t>Hunter.io</t>
         </is>
       </c>
       <c r="D83" s="44" t="inlineStr">
@@ -10885,12 +10978,12 @@
       </c>
       <c r="B84" s="47" t="inlineStr">
         <is>
-          <t>MILLIONVERIFIER_API_KEY</t>
+          <t>ZOOMINFO_USERNAME</t>
         </is>
       </c>
       <c r="C84" s="50" t="inlineStr">
         <is>
-          <t>MillionVerifier</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="D84" s="44" t="inlineStr">
@@ -10907,17 +11000,17 @@
     <row r="85">
       <c r="A85" s="44" t="inlineStr">
         <is>
-          <t>6. OUTBOUND SENDING  (AI Sequence Agent / AI SDR)</t>
+          <t>5. PROSPECTING &amp; DATA ENRICHMENT  (waterfall order = priority order)</t>
         </is>
       </c>
       <c r="B85" s="47" t="inlineStr">
         <is>
-          <t>OUTBOUND_PROVIDER</t>
+          <t>ZOOMINFO_PASSWORD</t>
         </is>
       </c>
       <c r="C85" s="50" t="inlineStr">
         <is>
-          <t>Instantly</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="D85" s="44" t="inlineStr">
@@ -10934,17 +11027,17 @@
     <row r="86">
       <c r="A86" s="44" t="inlineStr">
         <is>
-          <t>6. OUTBOUND SENDING  (AI Sequence Agent / AI SDR)</t>
+          <t>5. PROSPECTING &amp; DATA ENRICHMENT  (waterfall order = priority order)</t>
         </is>
       </c>
       <c r="B86" s="47" t="inlineStr">
         <is>
-          <t>INSTANTLY_API_KEY</t>
+          <t>ZOOMINFO_CLIENT_ID</t>
         </is>
       </c>
       <c r="C86" s="50" t="inlineStr">
         <is>
-          <t>Instantly</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="D86" s="44" t="inlineStr">
@@ -10961,17 +11054,17 @@
     <row r="87">
       <c r="A87" s="44" t="inlineStr">
         <is>
-          <t>6. OUTBOUND SENDING  (AI Sequence Agent / AI SDR)</t>
+          <t>5. PROSPECTING &amp; DATA ENRICHMENT  (waterfall order = priority order)</t>
         </is>
       </c>
       <c r="B87" s="47" t="inlineStr">
         <is>
-          <t>SMARTLEAD_API_KEY</t>
+          <t>ZOOMINFO_PRIVATE_KEY</t>
         </is>
       </c>
       <c r="C87" s="50" t="inlineStr">
         <is>
-          <t>Smartlead</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="D87" s="44" t="inlineStr">
@@ -10988,17 +11081,17 @@
     <row r="88">
       <c r="A88" s="44" t="inlineStr">
         <is>
-          <t>6. OUTBOUND SENDING  (AI Sequence Agent / AI SDR)</t>
+          <t>5. PROSPECTING &amp; DATA ENRICHMENT  (waterfall order = priority order)</t>
         </is>
       </c>
       <c r="B88" s="47" t="inlineStr">
         <is>
-          <t>LEMLIST_API_KEY</t>
+          <t>LUSHA_API_KEY</t>
         </is>
       </c>
       <c r="C88" s="50" t="inlineStr">
         <is>
-          <t>lemlist</t>
+          <t>Lusha (alternative enrichment)</t>
         </is>
       </c>
       <c r="D88" s="44" t="inlineStr">
@@ -11015,17 +11108,17 @@
     <row r="89">
       <c r="A89" s="44" t="inlineStr">
         <is>
-          <t>6. OUTBOUND SENDING  (AI Sequence Agent / AI SDR)</t>
+          <t>5. PROSPECTING &amp; DATA ENRICHMENT  (waterfall order = priority order)</t>
         </is>
       </c>
       <c r="B89" s="47" t="inlineStr">
         <is>
-          <t>SMTP_HOST</t>
+          <t>CRUNCHBASE_API_KEY</t>
         </is>
       </c>
       <c r="C89" s="50" t="inlineStr">
         <is>
-          <t>Your mailbox provider (native SMTP option)</t>
+          <t>Crunchbase</t>
         </is>
       </c>
       <c r="D89" s="44" t="inlineStr">
@@ -11042,17 +11135,17 @@
     <row r="90">
       <c r="A90" s="44" t="inlineStr">
         <is>
-          <t>6. OUTBOUND SENDING  (AI Sequence Agent / AI SDR)</t>
+          <t>5. PROSPECTING &amp; DATA ENRICHMENT  (waterfall order = priority order)</t>
         </is>
       </c>
       <c r="B90" s="47" t="inlineStr">
         <is>
-          <t>SMTP_PORT</t>
+          <t>BUILTWITH_API_KEY</t>
         </is>
       </c>
       <c r="C90" s="50" t="inlineStr">
         <is>
-          <t>Your mailbox provider (native SMTP option)</t>
+          <t>BuiltWith</t>
         </is>
       </c>
       <c r="D90" s="44" t="inlineStr">
@@ -11069,17 +11162,17 @@
     <row r="91">
       <c r="A91" s="44" t="inlineStr">
         <is>
-          <t>6. OUTBOUND SENDING  (AI Sequence Agent / AI SDR)</t>
+          <t>5. PROSPECTING &amp; DATA ENRICHMENT  (waterfall order = priority order)</t>
         </is>
       </c>
       <c r="B91" s="47" t="inlineStr">
         <is>
-          <t>SMTP_USER</t>
+          <t>PROXYCURL_API_KEY</t>
         </is>
       </c>
       <c r="C91" s="50" t="inlineStr">
         <is>
-          <t>Your mailbox provider (native SMTP option)</t>
+          <t>Proxycurl</t>
         </is>
       </c>
       <c r="D91" s="44" t="inlineStr">
@@ -11096,17 +11189,17 @@
     <row r="92">
       <c r="A92" s="44" t="inlineStr">
         <is>
-          <t>6. OUTBOUND SENDING  (AI Sequence Agent / AI SDR)</t>
+          <t>5. PROSPECTING &amp; DATA ENRICHMENT  (waterfall order = priority order)</t>
         </is>
       </c>
       <c r="B92" s="47" t="inlineStr">
         <is>
-          <t>SMTP_PASSWORD</t>
+          <t>EMAIL_VERIFICATION_WATERFALL</t>
         </is>
       </c>
       <c r="C92" s="50" t="inlineStr">
         <is>
-          <t>Your mailbox provider (native SMTP option)</t>
+          <t>MillionVerifier</t>
         </is>
       </c>
       <c r="D92" s="44" t="inlineStr">
@@ -11123,17 +11216,17 @@
     <row r="93">
       <c r="A93" s="44" t="inlineStr">
         <is>
-          <t>6. OUTBOUND SENDING  (AI Sequence Agent / AI SDR)</t>
+          <t>5. PROSPECTING &amp; DATA ENRICHMENT  (waterfall order = priority order)</t>
         </is>
       </c>
       <c r="B93" s="47" t="inlineStr">
         <is>
-          <t>SMTP_USE_TLS</t>
+          <t>ZEROBOUNCE_API_KEY</t>
         </is>
       </c>
       <c r="C93" s="50" t="inlineStr">
         <is>
-          <t>Your mailbox provider (native SMTP option)</t>
+          <t>ZeroBounce</t>
         </is>
       </c>
       <c r="D93" s="44" t="inlineStr">
@@ -11150,17 +11243,17 @@
     <row r="94">
       <c r="A94" s="44" t="inlineStr">
         <is>
-          <t>6. OUTBOUND SENDING  (AI Sequence Agent / AI SDR)</t>
+          <t>5. PROSPECTING &amp; DATA ENRICHMENT  (waterfall order = priority order)</t>
         </is>
       </c>
       <c r="B94" s="47" t="inlineStr">
         <is>
-          <t>GMAIL_CLIENT_ID</t>
+          <t>NEVERBOUNCE_API_KEY</t>
         </is>
       </c>
       <c r="C94" s="50" t="inlineStr">
         <is>
-          <t>Gmail API</t>
+          <t>NeverBounce</t>
         </is>
       </c>
       <c r="D94" s="44" t="inlineStr">
@@ -11177,17 +11270,17 @@
     <row r="95">
       <c r="A95" s="44" t="inlineStr">
         <is>
-          <t>6. OUTBOUND SENDING  (AI Sequence Agent / AI SDR)</t>
+          <t>5. PROSPECTING &amp; DATA ENRICHMENT  (waterfall order = priority order)</t>
         </is>
       </c>
       <c r="B95" s="47" t="inlineStr">
         <is>
-          <t>GMAIL_CLIENT_SECRET</t>
+          <t>MILLIONVERIFIER_API_KEY</t>
         </is>
       </c>
       <c r="C95" s="50" t="inlineStr">
         <is>
-          <t>Gmail API</t>
+          <t>MillionVerifier</t>
         </is>
       </c>
       <c r="D95" s="44" t="inlineStr">
@@ -11209,12 +11302,12 @@
       </c>
       <c r="B96" s="47" t="inlineStr">
         <is>
-          <t>GMAIL_REFRESH_TOKEN</t>
+          <t>OUTBOUND_PROVIDER</t>
         </is>
       </c>
       <c r="C96" s="50" t="inlineStr">
         <is>
-          <t>Gmail API</t>
+          <t>Instantly</t>
         </is>
       </c>
       <c r="D96" s="44" t="inlineStr">
@@ -11236,12 +11329,12 @@
       </c>
       <c r="B97" s="47" t="inlineStr">
         <is>
-          <t>MS_GRAPH_TENANT_ID</t>
+          <t>INSTANTLY_API_KEY</t>
         </is>
       </c>
       <c r="C97" s="50" t="inlineStr">
         <is>
-          <t>Microsoft Graph</t>
+          <t>Instantly</t>
         </is>
       </c>
       <c r="D97" s="44" t="inlineStr">
@@ -11263,12 +11356,12 @@
       </c>
       <c r="B98" s="47" t="inlineStr">
         <is>
-          <t>MS_GRAPH_CLIENT_ID</t>
+          <t>SMARTLEAD_API_KEY</t>
         </is>
       </c>
       <c r="C98" s="50" t="inlineStr">
         <is>
-          <t>Microsoft Graph</t>
+          <t>Smartlead</t>
         </is>
       </c>
       <c r="D98" s="44" t="inlineStr">
@@ -11290,12 +11383,12 @@
       </c>
       <c r="B99" s="47" t="inlineStr">
         <is>
-          <t>MS_GRAPH_CLIENT_SECRET</t>
+          <t>LEMLIST_API_KEY</t>
         </is>
       </c>
       <c r="C99" s="50" t="inlineStr">
         <is>
-          <t>Microsoft Graph</t>
+          <t>lemlist</t>
         </is>
       </c>
       <c r="D99" s="44" t="inlineStr">
@@ -11317,12 +11410,12 @@
       </c>
       <c r="B100" s="47" t="inlineStr">
         <is>
-          <t>OUTBOUND_DAILY_LIMIT_PER_MAILBOX</t>
+          <t>SMTP_HOST</t>
         </is>
       </c>
       <c r="C100" s="50" t="inlineStr">
         <is>
-          <t>Instantly</t>
+          <t>Your mailbox provider (native SMTP option)</t>
         </is>
       </c>
       <c r="D100" s="44" t="inlineStr">
@@ -11344,12 +11437,12 @@
       </c>
       <c r="B101" s="47" t="inlineStr">
         <is>
-          <t>CALENDLY_API_KEY</t>
+          <t>SMTP_PORT</t>
         </is>
       </c>
       <c r="C101" s="50" t="inlineStr">
         <is>
-          <t>Calendly</t>
+          <t>Your mailbox provider (native SMTP option)</t>
         </is>
       </c>
       <c r="D101" s="44" t="inlineStr">
@@ -11371,12 +11464,12 @@
       </c>
       <c r="B102" s="47" t="inlineStr">
         <is>
-          <t>CAL_COM_API_KEY</t>
+          <t>SMTP_USER</t>
         </is>
       </c>
       <c r="C102" s="50" t="inlineStr">
         <is>
-          <t>Cal.com</t>
+          <t>Your mailbox provider (native SMTP option)</t>
         </is>
       </c>
       <c r="D102" s="44" t="inlineStr">
@@ -11398,12 +11491,12 @@
       </c>
       <c r="B103" s="47" t="inlineStr">
         <is>
-          <t>GOOGLE_CALENDAR_CLIENT_ID</t>
+          <t>SMTP_PASSWORD</t>
         </is>
       </c>
       <c r="C103" s="50" t="inlineStr">
         <is>
-          <t>Google Cloud (same project as GA4)</t>
+          <t>Your mailbox provider (native SMTP option)</t>
         </is>
       </c>
       <c r="D103" s="44" t="inlineStr">
@@ -11425,12 +11518,12 @@
       </c>
       <c r="B104" s="47" t="inlineStr">
         <is>
-          <t>GOOGLE_CALENDAR_CLIENT_SECRET</t>
+          <t>SMTP_USE_TLS</t>
         </is>
       </c>
       <c r="C104" s="50" t="inlineStr">
         <is>
-          <t>Google Cloud (same project as GA4)</t>
+          <t>Your mailbox provider (native SMTP option)</t>
         </is>
       </c>
       <c r="D104" s="44" t="inlineStr">
@@ -11447,17 +11540,17 @@
     <row r="105">
       <c r="A105" s="44" t="inlineStr">
         <is>
-          <t>7. EMAIL MARKETING / LIFECYCLE / WHATSAPP</t>
+          <t>6. OUTBOUND SENDING  (AI Sequence Agent / AI SDR)</t>
         </is>
       </c>
       <c r="B105" s="47" t="inlineStr">
         <is>
-          <t>ESP_PROVIDER</t>
+          <t>GMAIL_CLIENT_ID</t>
         </is>
       </c>
       <c r="C105" s="50" t="inlineStr">
         <is>
-          <t>Resend</t>
+          <t>Gmail API</t>
         </is>
       </c>
       <c r="D105" s="44" t="inlineStr">
@@ -11474,17 +11567,17 @@
     <row r="106">
       <c r="A106" s="44" t="inlineStr">
         <is>
-          <t>7. EMAIL MARKETING / LIFECYCLE / WHATSAPP</t>
+          <t>6. OUTBOUND SENDING  (AI Sequence Agent / AI SDR)</t>
         </is>
       </c>
       <c r="B106" s="47" t="inlineStr">
         <is>
-          <t>SENDGRID_API_KEY</t>
+          <t>GMAIL_CLIENT_SECRET</t>
         </is>
       </c>
       <c r="C106" s="50" t="inlineStr">
         <is>
-          <t>SendGrid</t>
+          <t>Gmail API</t>
         </is>
       </c>
       <c r="D106" s="44" t="inlineStr">
@@ -11501,17 +11594,17 @@
     <row r="107">
       <c r="A107" s="44" t="inlineStr">
         <is>
-          <t>7. EMAIL MARKETING / LIFECYCLE / WHATSAPP</t>
+          <t>6. OUTBOUND SENDING  (AI Sequence Agent / AI SDR)</t>
         </is>
       </c>
       <c r="B107" s="47" t="inlineStr">
         <is>
-          <t>RESEND_API_KEY</t>
+          <t>GMAIL_REFRESH_TOKEN</t>
         </is>
       </c>
       <c r="C107" s="50" t="inlineStr">
         <is>
-          <t>Resend</t>
+          <t>Gmail API</t>
         </is>
       </c>
       <c r="D107" s="44" t="inlineStr">
@@ -11528,17 +11621,17 @@
     <row r="108">
       <c r="A108" s="44" t="inlineStr">
         <is>
-          <t>7. EMAIL MARKETING / LIFECYCLE / WHATSAPP</t>
+          <t>6. OUTBOUND SENDING  (AI Sequence Agent / AI SDR)</t>
         </is>
       </c>
       <c r="B108" s="47" t="inlineStr">
         <is>
-          <t>MAILCHIMP_API_KEY</t>
+          <t>MS_GRAPH_TENANT_ID</t>
         </is>
       </c>
       <c r="C108" s="50" t="inlineStr">
         <is>
-          <t>Mailchimp</t>
+          <t>Microsoft Graph</t>
         </is>
       </c>
       <c r="D108" s="44" t="inlineStr">
@@ -11555,17 +11648,17 @@
     <row r="109">
       <c r="A109" s="44" t="inlineStr">
         <is>
-          <t>7. EMAIL MARKETING / LIFECYCLE / WHATSAPP</t>
+          <t>6. OUTBOUND SENDING  (AI Sequence Agent / AI SDR)</t>
         </is>
       </c>
       <c r="B109" s="47" t="inlineStr">
         <is>
-          <t>MAILCHIMP_SERVER_PREFIX</t>
+          <t>MS_GRAPH_CLIENT_ID</t>
         </is>
       </c>
       <c r="C109" s="50" t="inlineStr">
         <is>
-          <t>Mailchimp</t>
+          <t>Microsoft Graph</t>
         </is>
       </c>
       <c r="D109" s="44" t="inlineStr">
@@ -11582,17 +11675,17 @@
     <row r="110">
       <c r="A110" s="44" t="inlineStr">
         <is>
-          <t>7. EMAIL MARKETING / LIFECYCLE / WHATSAPP</t>
+          <t>6. OUTBOUND SENDING  (AI Sequence Agent / AI SDR)</t>
         </is>
       </c>
       <c r="B110" s="47" t="inlineStr">
         <is>
-          <t>KLAVIYO_API_KEY</t>
+          <t>MS_GRAPH_CLIENT_SECRET</t>
         </is>
       </c>
       <c r="C110" s="50" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Microsoft Graph</t>
         </is>
       </c>
       <c r="D110" s="44" t="inlineStr">
@@ -11609,17 +11702,17 @@
     <row r="111">
       <c r="A111" s="44" t="inlineStr">
         <is>
-          <t>7. EMAIL MARKETING / LIFECYCLE / WHATSAPP</t>
+          <t>6. OUTBOUND SENDING  (AI Sequence Agent / AI SDR)</t>
         </is>
       </c>
       <c r="B111" s="47" t="inlineStr">
         <is>
-          <t>BREVO_API_KEY</t>
+          <t>OUTBOUND_DAILY_LIMIT_PER_MAILBOX</t>
         </is>
       </c>
       <c r="C111" s="50" t="inlineStr">
         <is>
-          <t>Brevo</t>
+          <t>Instantly</t>
         </is>
       </c>
       <c r="D111" s="44" t="inlineStr">
@@ -11636,17 +11729,17 @@
     <row r="112">
       <c r="A112" s="44" t="inlineStr">
         <is>
-          <t>7. EMAIL MARKETING / LIFECYCLE / WHATSAPP</t>
+          <t>6. OUTBOUND SENDING  (AI Sequence Agent / AI SDR)</t>
         </is>
       </c>
       <c r="B112" s="47" t="inlineStr">
         <is>
-          <t>DEFAULT_FROM_EMAIL</t>
+          <t>CALENDLY_API_KEY</t>
         </is>
       </c>
       <c r="C112" s="50" t="inlineStr">
         <is>
-          <t>Resend</t>
+          <t>Calendly</t>
         </is>
       </c>
       <c r="D112" s="44" t="inlineStr">
@@ -11663,17 +11756,17 @@
     <row r="113">
       <c r="A113" s="44" t="inlineStr">
         <is>
-          <t>7. EMAIL MARKETING / LIFECYCLE / WHATSAPP</t>
+          <t>6. OUTBOUND SENDING  (AI Sequence Agent / AI SDR)</t>
         </is>
       </c>
       <c r="B113" s="47" t="inlineStr">
         <is>
-          <t>WHATSAPP_PHONE_NUMBER_ID</t>
+          <t>CAL_COM_API_KEY</t>
         </is>
       </c>
       <c r="C113" s="50" t="inlineStr">
         <is>
-          <t>WhatsApp Business Cloud API</t>
+          <t>Cal.com</t>
         </is>
       </c>
       <c r="D113" s="44" t="inlineStr">
@@ -11690,17 +11783,17 @@
     <row r="114">
       <c r="A114" s="44" t="inlineStr">
         <is>
-          <t>7. EMAIL MARKETING / LIFECYCLE / WHATSAPP</t>
+          <t>6. OUTBOUND SENDING  (AI Sequence Agent / AI SDR)</t>
         </is>
       </c>
       <c r="B114" s="47" t="inlineStr">
         <is>
-          <t>WHATSAPP_BUSINESS_ACCOUNT_ID</t>
+          <t>GOOGLE_CALENDAR_CLIENT_ID</t>
         </is>
       </c>
       <c r="C114" s="50" t="inlineStr">
         <is>
-          <t>WhatsApp Business Cloud API</t>
+          <t>Google Cloud (same project as GA4)</t>
         </is>
       </c>
       <c r="D114" s="44" t="inlineStr">
@@ -11717,17 +11810,17 @@
     <row r="115">
       <c r="A115" s="44" t="inlineStr">
         <is>
-          <t>7. EMAIL MARKETING / LIFECYCLE / WHATSAPP</t>
+          <t>6. OUTBOUND SENDING  (AI Sequence Agent / AI SDR)</t>
         </is>
       </c>
       <c r="B115" s="47" t="inlineStr">
         <is>
-          <t>WHATSAPP_ACCESS_TOKEN</t>
+          <t>GOOGLE_CALENDAR_CLIENT_SECRET</t>
         </is>
       </c>
       <c r="C115" s="50" t="inlineStr">
         <is>
-          <t>WhatsApp Business Cloud API</t>
+          <t>Google Cloud (same project as GA4)</t>
         </is>
       </c>
       <c r="D115" s="44" t="inlineStr">
@@ -11749,12 +11842,12 @@
       </c>
       <c r="B116" s="47" t="inlineStr">
         <is>
-          <t>WHATSAPP_WEBHOOK_VERIFY_TOKEN</t>
+          <t>ESP_PROVIDER</t>
         </is>
       </c>
       <c r="C116" s="50" t="inlineStr">
         <is>
-          <t>You invent this string (must match Meta)</t>
+          <t>Resend</t>
         </is>
       </c>
       <c r="D116" s="44" t="inlineStr">
@@ -11776,12 +11869,12 @@
       </c>
       <c r="B117" s="47" t="inlineStr">
         <is>
-          <t>TWILIO_ACCOUNT_SID</t>
+          <t>SENDGRID_API_KEY</t>
         </is>
       </c>
       <c r="C117" s="50" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>SendGrid</t>
         </is>
       </c>
       <c r="D117" s="44" t="inlineStr">
@@ -11803,12 +11896,12 @@
       </c>
       <c r="B118" s="47" t="inlineStr">
         <is>
-          <t>TWILIO_AUTH_TOKEN</t>
+          <t>RESEND_API_KEY</t>
         </is>
       </c>
       <c r="C118" s="50" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Resend</t>
         </is>
       </c>
       <c r="D118" s="44" t="inlineStr">
@@ -11830,12 +11923,12 @@
       </c>
       <c r="B119" s="47" t="inlineStr">
         <is>
-          <t>TWILIO_FROM_NUMBER</t>
+          <t>MAILCHIMP_API_KEY</t>
         </is>
       </c>
       <c r="C119" s="50" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Mailchimp</t>
         </is>
       </c>
       <c r="D119" s="44" t="inlineStr">
@@ -11852,17 +11945,17 @@
     <row r="120">
       <c r="A120" s="44" t="inlineStr">
         <is>
-          <t>8. CRM  (CRM Agent)</t>
+          <t>7. EMAIL MARKETING / LIFECYCLE / WHATSAPP</t>
         </is>
       </c>
       <c r="B120" s="47" t="inlineStr">
         <is>
-          <t>CRM_PROVIDER</t>
+          <t>MAILCHIMP_SERVER_PREFIX</t>
         </is>
       </c>
       <c r="C120" s="50" t="inlineStr">
         <is>
-          <t>HubSpot</t>
+          <t>Mailchimp</t>
         </is>
       </c>
       <c r="D120" s="44" t="inlineStr">
@@ -11879,17 +11972,17 @@
     <row r="121">
       <c r="A121" s="44" t="inlineStr">
         <is>
-          <t>8. CRM  (CRM Agent)</t>
+          <t>7. EMAIL MARKETING / LIFECYCLE / WHATSAPP</t>
         </is>
       </c>
       <c r="B121" s="47" t="inlineStr">
         <is>
-          <t>HUBSPOT_ACCESS_TOKEN</t>
+          <t>KLAVIYO_API_KEY</t>
         </is>
       </c>
       <c r="C121" s="50" t="inlineStr">
         <is>
-          <t>HubSpot</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="D121" s="44" t="inlineStr">
@@ -11906,17 +11999,17 @@
     <row r="122">
       <c r="A122" s="44" t="inlineStr">
         <is>
-          <t>8. CRM  (CRM Agent)</t>
+          <t>7. EMAIL MARKETING / LIFECYCLE / WHATSAPP</t>
         </is>
       </c>
       <c r="B122" s="47" t="inlineStr">
         <is>
-          <t>HUBSPOT_CLIENT_ID</t>
+          <t>BREVO_API_KEY</t>
         </is>
       </c>
       <c r="C122" s="50" t="inlineStr">
         <is>
-          <t>HubSpot (only for OAuth apps, not private apps)</t>
+          <t>Brevo</t>
         </is>
       </c>
       <c r="D122" s="44" t="inlineStr">
@@ -11933,17 +12026,17 @@
     <row r="123">
       <c r="A123" s="44" t="inlineStr">
         <is>
-          <t>8. CRM  (CRM Agent)</t>
+          <t>7. EMAIL MARKETING / LIFECYCLE / WHATSAPP</t>
         </is>
       </c>
       <c r="B123" s="47" t="inlineStr">
         <is>
-          <t>HUBSPOT_CLIENT_SECRET</t>
+          <t>DEFAULT_FROM_EMAIL</t>
         </is>
       </c>
       <c r="C123" s="50" t="inlineStr">
         <is>
-          <t>HubSpot (only for OAuth apps, not private apps)</t>
+          <t>Resend</t>
         </is>
       </c>
       <c r="D123" s="44" t="inlineStr">
@@ -11960,17 +12053,17 @@
     <row r="124">
       <c r="A124" s="44" t="inlineStr">
         <is>
-          <t>8. CRM  (CRM Agent)</t>
+          <t>7. EMAIL MARKETING / LIFECYCLE / WHATSAPP</t>
         </is>
       </c>
       <c r="B124" s="47" t="inlineStr">
         <is>
-          <t>HUBSPOT_PORTAL_ID</t>
+          <t>WHATSAPP_PHONE_NUMBER_ID</t>
         </is>
       </c>
       <c r="C124" s="50" t="inlineStr">
         <is>
-          <t>HubSpot</t>
+          <t>WhatsApp Business Cloud API</t>
         </is>
       </c>
       <c r="D124" s="44" t="inlineStr">
@@ -11987,17 +12080,17 @@
     <row r="125">
       <c r="A125" s="44" t="inlineStr">
         <is>
-          <t>8. CRM  (CRM Agent)</t>
+          <t>7. EMAIL MARKETING / LIFECYCLE / WHATSAPP</t>
         </is>
       </c>
       <c r="B125" s="47" t="inlineStr">
         <is>
-          <t>SALESFORCE_CLIENT_ID</t>
+          <t>WHATSAPP_BUSINESS_ACCOUNT_ID</t>
         </is>
       </c>
       <c r="C125" s="50" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>WhatsApp Business Cloud API</t>
         </is>
       </c>
       <c r="D125" s="44" t="inlineStr">
@@ -12014,17 +12107,17 @@
     <row r="126">
       <c r="A126" s="44" t="inlineStr">
         <is>
-          <t>8. CRM  (CRM Agent)</t>
+          <t>7. EMAIL MARKETING / LIFECYCLE / WHATSAPP</t>
         </is>
       </c>
       <c r="B126" s="47" t="inlineStr">
         <is>
-          <t>SALESFORCE_CLIENT_SECRET</t>
+          <t>WHATSAPP_ACCESS_TOKEN</t>
         </is>
       </c>
       <c r="C126" s="50" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>WhatsApp Business Cloud API</t>
         </is>
       </c>
       <c r="D126" s="44" t="inlineStr">
@@ -12041,17 +12134,17 @@
     <row r="127">
       <c r="A127" s="44" t="inlineStr">
         <is>
-          <t>8. CRM  (CRM Agent)</t>
+          <t>7. EMAIL MARKETING / LIFECYCLE / WHATSAPP</t>
         </is>
       </c>
       <c r="B127" s="47" t="inlineStr">
         <is>
-          <t>SALESFORCE_USERNAME</t>
+          <t>WHATSAPP_WEBHOOK_VERIFY_TOKEN</t>
         </is>
       </c>
       <c r="C127" s="50" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>You invent this string (must match Meta)</t>
         </is>
       </c>
       <c r="D127" s="44" t="inlineStr">
@@ -12068,17 +12161,17 @@
     <row r="128">
       <c r="A128" s="44" t="inlineStr">
         <is>
-          <t>8. CRM  (CRM Agent)</t>
+          <t>7. EMAIL MARKETING / LIFECYCLE / WHATSAPP</t>
         </is>
       </c>
       <c r="B128" s="47" t="inlineStr">
         <is>
-          <t>SALESFORCE_PASSWORD</t>
+          <t>TWILIO_ACCOUNT_SID</t>
         </is>
       </c>
       <c r="C128" s="50" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="D128" s="44" t="inlineStr">
@@ -12095,17 +12188,17 @@
     <row r="129">
       <c r="A129" s="44" t="inlineStr">
         <is>
-          <t>8. CRM  (CRM Agent)</t>
+          <t>7. EMAIL MARKETING / LIFECYCLE / WHATSAPP</t>
         </is>
       </c>
       <c r="B129" s="47" t="inlineStr">
         <is>
-          <t>SALESFORCE_SECURITY_TOKEN</t>
+          <t>TWILIO_AUTH_TOKEN</t>
         </is>
       </c>
       <c r="C129" s="50" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="D129" s="44" t="inlineStr">
@@ -12122,17 +12215,17 @@
     <row r="130">
       <c r="A130" s="44" t="inlineStr">
         <is>
-          <t>8. CRM  (CRM Agent)</t>
+          <t>7. EMAIL MARKETING / LIFECYCLE / WHATSAPP</t>
         </is>
       </c>
       <c r="B130" s="47" t="inlineStr">
         <is>
-          <t>SALESFORCE_INSTANCE_URL</t>
+          <t>TWILIO_FROM_NUMBER</t>
         </is>
       </c>
       <c r="C130" s="50" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="D130" s="44" t="inlineStr">
@@ -12154,12 +12247,12 @@
       </c>
       <c r="B131" s="47" t="inlineStr">
         <is>
-          <t>PIPEDRIVE_API_TOKEN</t>
+          <t>CRM_PROVIDER</t>
         </is>
       </c>
       <c r="C131" s="50" t="inlineStr">
         <is>
-          <t>Pipedrive</t>
+          <t>HubSpot</t>
         </is>
       </c>
       <c r="D131" s="44" t="inlineStr">
@@ -12181,12 +12274,12 @@
       </c>
       <c r="B132" s="47" t="inlineStr">
         <is>
-          <t>PIPEDRIVE_COMPANY_DOMAIN</t>
+          <t>HUBSPOT_ACCESS_TOKEN</t>
         </is>
       </c>
       <c r="C132" s="50" t="inlineStr">
         <is>
-          <t>Pipedrive</t>
+          <t>HubSpot</t>
         </is>
       </c>
       <c r="D132" s="44" t="inlineStr">
@@ -12203,17 +12296,17 @@
     <row r="133">
       <c r="A133" s="44" t="inlineStr">
         <is>
-          <t>9. ANALYTICS, ATTRIBUTION &amp; REVENUE</t>
+          <t>8. CRM  (CRM Agent)</t>
         </is>
       </c>
       <c r="B133" s="47" t="inlineStr">
         <is>
-          <t>GA4_PROPERTY_ID</t>
+          <t>HUBSPOT_CLIENT_ID</t>
         </is>
       </c>
       <c r="C133" s="50" t="inlineStr">
         <is>
-          <t>Google Analytics 4</t>
+          <t>HubSpot (only for OAuth apps, not private apps)</t>
         </is>
       </c>
       <c r="D133" s="44" t="inlineStr">
@@ -12230,17 +12323,17 @@
     <row r="134">
       <c r="A134" s="44" t="inlineStr">
         <is>
-          <t>9. ANALYTICS, ATTRIBUTION &amp; REVENUE</t>
+          <t>8. CRM  (CRM Agent)</t>
         </is>
       </c>
       <c r="B134" s="47" t="inlineStr">
         <is>
-          <t>GOOGLE_SERVICE_ACCOUNT_JSON_PATH</t>
+          <t>HUBSPOT_CLIENT_SECRET</t>
         </is>
       </c>
       <c r="C134" s="50" t="inlineStr">
         <is>
-          <t>Google Analytics 4</t>
+          <t>HubSpot (only for OAuth apps, not private apps)</t>
         </is>
       </c>
       <c r="D134" s="44" t="inlineStr">
@@ -12257,17 +12350,17 @@
     <row r="135">
       <c r="A135" s="44" t="inlineStr">
         <is>
-          <t>9. ANALYTICS, ATTRIBUTION &amp; REVENUE</t>
+          <t>8. CRM  (CRM Agent)</t>
         </is>
       </c>
       <c r="B135" s="47" t="inlineStr">
         <is>
-          <t>GOOGLE_SERVICE_ACCOUNT_JSON</t>
+          <t>HUBSPOT_PORTAL_ID</t>
         </is>
       </c>
       <c r="C135" s="50" t="inlineStr">
         <is>
-          <t>Google Cloud service account (inline JSON)</t>
+          <t>HubSpot</t>
         </is>
       </c>
       <c r="D135" s="44" t="inlineStr">
@@ -12284,17 +12377,17 @@
     <row r="136">
       <c r="A136" s="44" t="inlineStr">
         <is>
-          <t>9. ANALYTICS, ATTRIBUTION &amp; REVENUE</t>
+          <t>8. CRM  (CRM Agent)</t>
         </is>
       </c>
       <c r="B136" s="47" t="inlineStr">
         <is>
-          <t>GSC_SITE_URL</t>
+          <t>SALESFORCE_CLIENT_ID</t>
         </is>
       </c>
       <c r="C136" s="50" t="inlineStr">
         <is>
-          <t>Google Search Console</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="D136" s="44" t="inlineStr">
@@ -12311,17 +12404,17 @@
     <row r="137">
       <c r="A137" s="44" t="inlineStr">
         <is>
-          <t>9. ANALYTICS, ATTRIBUTION &amp; REVENUE</t>
+          <t>8. CRM  (CRM Agent)</t>
         </is>
       </c>
       <c r="B137" s="47" t="inlineStr">
         <is>
-          <t>STRIPE_SECRET_KEY</t>
+          <t>SALESFORCE_CLIENT_SECRET</t>
         </is>
       </c>
       <c r="C137" s="50" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="D137" s="44" t="inlineStr">
@@ -12338,17 +12431,17 @@
     <row r="138">
       <c r="A138" s="44" t="inlineStr">
         <is>
-          <t>9. ANALYTICS, ATTRIBUTION &amp; REVENUE</t>
+          <t>8. CRM  (CRM Agent)</t>
         </is>
       </c>
       <c r="B138" s="47" t="inlineStr">
         <is>
-          <t>STRIPE_WEBHOOK_SECRET</t>
+          <t>SALESFORCE_USERNAME</t>
         </is>
       </c>
       <c r="C138" s="50" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="D138" s="44" t="inlineStr">
@@ -12365,17 +12458,17 @@
     <row r="139">
       <c r="A139" s="44" t="inlineStr">
         <is>
-          <t>9. ANALYTICS, ATTRIBUTION &amp; REVENUE</t>
+          <t>8. CRM  (CRM Agent)</t>
         </is>
       </c>
       <c r="B139" s="47" t="inlineStr">
         <is>
-          <t>SHOPIFY_STORE_DOMAIN</t>
+          <t>SALESFORCE_PASSWORD</t>
         </is>
       </c>
       <c r="C139" s="50" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="D139" s="44" t="inlineStr">
@@ -12392,17 +12485,17 @@
     <row r="140">
       <c r="A140" s="44" t="inlineStr">
         <is>
-          <t>9. ANALYTICS, ATTRIBUTION &amp; REVENUE</t>
+          <t>8. CRM  (CRM Agent)</t>
         </is>
       </c>
       <c r="B140" s="47" t="inlineStr">
         <is>
-          <t>SHOPIFY_ADMIN_ACCESS_TOKEN</t>
+          <t>SALESFORCE_SECURITY_TOKEN</t>
         </is>
       </c>
       <c r="C140" s="50" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="D140" s="44" t="inlineStr">
@@ -12419,17 +12512,17 @@
     <row r="141">
       <c r="A141" s="44" t="inlineStr">
         <is>
-          <t>9. ANALYTICS, ATTRIBUTION &amp; REVENUE</t>
+          <t>8. CRM  (CRM Agent)</t>
         </is>
       </c>
       <c r="B141" s="47" t="inlineStr">
         <is>
-          <t>SHOPIFY_API_VERSION</t>
+          <t>SALESFORCE_INSTANCE_URL</t>
         </is>
       </c>
       <c r="C141" s="50" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="D141" s="44" t="inlineStr">
@@ -12446,17 +12539,17 @@
     <row r="142">
       <c r="A142" s="44" t="inlineStr">
         <is>
-          <t>9. ANALYTICS, ATTRIBUTION &amp; REVENUE</t>
+          <t>8. CRM  (CRM Agent)</t>
         </is>
       </c>
       <c r="B142" s="47" t="inlineStr">
         <is>
-          <t>SEGMENT_WRITE_KEY</t>
+          <t>PIPEDRIVE_API_TOKEN</t>
         </is>
       </c>
       <c r="C142" s="50" t="inlineStr">
         <is>
-          <t>Segment</t>
+          <t>Pipedrive</t>
         </is>
       </c>
       <c r="D142" s="44" t="inlineStr">
@@ -12473,17 +12566,17 @@
     <row r="143">
       <c r="A143" s="44" t="inlineStr">
         <is>
-          <t>9. ANALYTICS, ATTRIBUTION &amp; REVENUE</t>
+          <t>8. CRM  (CRM Agent)</t>
         </is>
       </c>
       <c r="B143" s="47" t="inlineStr">
         <is>
-          <t>MIXPANEL_PROJECT_TOKEN</t>
+          <t>PIPEDRIVE_COMPANY_DOMAIN</t>
         </is>
       </c>
       <c r="C143" s="50" t="inlineStr">
         <is>
-          <t>Mixpanel</t>
+          <t>Pipedrive</t>
         </is>
       </c>
       <c r="D143" s="44" t="inlineStr">
@@ -12505,12 +12598,12 @@
       </c>
       <c r="B144" s="47" t="inlineStr">
         <is>
-          <t>POSTHOG_API_KEY</t>
+          <t>GA4_PROPERTY_ID</t>
         </is>
       </c>
       <c r="C144" s="50" t="inlineStr">
         <is>
-          <t>PostHog</t>
+          <t>Google Analytics 4</t>
         </is>
       </c>
       <c r="D144" s="44" t="inlineStr">
@@ -12532,12 +12625,12 @@
       </c>
       <c r="B145" s="47" t="inlineStr">
         <is>
-          <t>POSTHOG_HOST</t>
+          <t>GOOGLE_SERVICE_ACCOUNT_JSON_PATH</t>
         </is>
       </c>
       <c r="C145" s="50" t="inlineStr">
         <is>
-          <t>PostHog</t>
+          <t>Google Analytics 4</t>
         </is>
       </c>
       <c r="D145" s="44" t="inlineStr">
@@ -12559,12 +12652,12 @@
       </c>
       <c r="B146" s="47" t="inlineStr">
         <is>
-          <t>BIGQUERY_PROJECT_ID</t>
+          <t>GOOGLE_SERVICE_ACCOUNT_JSON</t>
         </is>
       </c>
       <c r="C146" s="50" t="inlineStr">
         <is>
-          <t>Google Cloud (optional warehouse)</t>
+          <t>Google Cloud service account (inline JSON)</t>
         </is>
       </c>
       <c r="D146" s="44" t="inlineStr">
@@ -12586,12 +12679,12 @@
       </c>
       <c r="B147" s="47" t="inlineStr">
         <is>
-          <t>BIGQUERY_DATASET</t>
+          <t>GSC_SITE_URL</t>
         </is>
       </c>
       <c r="C147" s="50" t="inlineStr">
         <is>
-          <t>Google Cloud (optional warehouse)</t>
+          <t>Google Search Console</t>
         </is>
       </c>
       <c r="D147" s="44" t="inlineStr">
@@ -12613,12 +12706,12 @@
       </c>
       <c r="B148" s="47" t="inlineStr">
         <is>
-          <t>SNOWFLAKE_ACCOUNT</t>
+          <t>STRIPE_SECRET_KEY</t>
         </is>
       </c>
       <c r="C148" s="50" t="inlineStr">
         <is>
-          <t>Snowflake (optional warehouse)</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D148" s="44" t="inlineStr">
@@ -12640,12 +12733,12 @@
       </c>
       <c r="B149" s="47" t="inlineStr">
         <is>
-          <t>SNOWFLAKE_USER</t>
+          <t>STRIPE_WEBHOOK_SECRET</t>
         </is>
       </c>
       <c r="C149" s="50" t="inlineStr">
         <is>
-          <t>Snowflake (optional warehouse)</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="D149" s="44" t="inlineStr">
@@ -12667,12 +12760,12 @@
       </c>
       <c r="B150" s="47" t="inlineStr">
         <is>
-          <t>SNOWFLAKE_PASSWORD</t>
+          <t>SHOPIFY_STORE_DOMAIN</t>
         </is>
       </c>
       <c r="C150" s="50" t="inlineStr">
         <is>
-          <t>Snowflake (optional warehouse)</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="D150" s="44" t="inlineStr">
@@ -12689,17 +12782,17 @@
     <row r="151">
       <c r="A151" s="44" t="inlineStr">
         <is>
-          <t>10. SEO &amp; CONTENT INTELLIGENCE  (SEO Agent, Market / Competitor Intelligence)</t>
+          <t>9. ANALYTICS, ATTRIBUTION &amp; REVENUE</t>
         </is>
       </c>
       <c r="B151" s="47" t="inlineStr">
         <is>
-          <t>SEMRUSH_API_KEY</t>
+          <t>SHOPIFY_ADMIN_ACCESS_TOKEN</t>
         </is>
       </c>
       <c r="C151" s="50" t="inlineStr">
         <is>
-          <t>Semrush</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="D151" s="44" t="inlineStr">
@@ -12716,17 +12809,17 @@
     <row r="152">
       <c r="A152" s="44" t="inlineStr">
         <is>
-          <t>10. SEO &amp; CONTENT INTELLIGENCE  (SEO Agent, Market / Competitor Intelligence)</t>
+          <t>9. ANALYTICS, ATTRIBUTION &amp; REVENUE</t>
         </is>
       </c>
       <c r="B152" s="47" t="inlineStr">
         <is>
-          <t>AHREFS_API_KEY</t>
+          <t>SHOPIFY_API_VERSION</t>
         </is>
       </c>
       <c r="C152" s="50" t="inlineStr">
         <is>
-          <t>Ahrefs</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="D152" s="44" t="inlineStr">
@@ -12743,17 +12836,17 @@
     <row r="153">
       <c r="A153" s="44" t="inlineStr">
         <is>
-          <t>10. SEO &amp; CONTENT INTELLIGENCE  (SEO Agent, Market / Competitor Intelligence)</t>
+          <t>9. ANALYTICS, ATTRIBUTION &amp; REVENUE</t>
         </is>
       </c>
       <c r="B153" s="47" t="inlineStr">
         <is>
-          <t>SERPAPI_API_KEY</t>
+          <t>SEGMENT_WRITE_KEY</t>
         </is>
       </c>
       <c r="C153" s="50" t="inlineStr">
         <is>
-          <t>SerpApi</t>
+          <t>Segment</t>
         </is>
       </c>
       <c r="D153" s="44" t="inlineStr">
@@ -12770,17 +12863,17 @@
     <row r="154">
       <c r="A154" s="44" t="inlineStr">
         <is>
-          <t>10. SEO &amp; CONTENT INTELLIGENCE  (SEO Agent, Market / Competitor Intelligence)</t>
+          <t>9. ANALYTICS, ATTRIBUTION &amp; REVENUE</t>
         </is>
       </c>
       <c r="B154" s="47" t="inlineStr">
         <is>
-          <t>DATAFORSEO_LOGIN</t>
+          <t>MIXPANEL_PROJECT_TOKEN</t>
         </is>
       </c>
       <c r="C154" s="50" t="inlineStr">
         <is>
-          <t>DataForSEO</t>
+          <t>Mixpanel</t>
         </is>
       </c>
       <c r="D154" s="44" t="inlineStr">
@@ -12797,17 +12890,17 @@
     <row r="155">
       <c r="A155" s="44" t="inlineStr">
         <is>
-          <t>10. SEO &amp; CONTENT INTELLIGENCE  (SEO Agent, Market / Competitor Intelligence)</t>
+          <t>9. ANALYTICS, ATTRIBUTION &amp; REVENUE</t>
         </is>
       </c>
       <c r="B155" s="47" t="inlineStr">
         <is>
-          <t>DATAFORSEO_PASSWORD</t>
+          <t>POSTHOG_API_KEY</t>
         </is>
       </c>
       <c r="C155" s="50" t="inlineStr">
         <is>
-          <t>DataForSEO</t>
+          <t>PostHog</t>
         </is>
       </c>
       <c r="D155" s="44" t="inlineStr">
@@ -12824,17 +12917,17 @@
     <row r="156">
       <c r="A156" s="44" t="inlineStr">
         <is>
-          <t>10. SEO &amp; CONTENT INTELLIGENCE  (SEO Agent, Market / Competitor Intelligence)</t>
+          <t>9. ANALYTICS, ATTRIBUTION &amp; REVENUE</t>
         </is>
       </c>
       <c r="B156" s="47" t="inlineStr">
         <is>
-          <t>FIRECRAWL_API_KEY</t>
+          <t>POSTHOG_HOST</t>
         </is>
       </c>
       <c r="C156" s="50" t="inlineStr">
         <is>
-          <t>Firecrawl</t>
+          <t>PostHog</t>
         </is>
       </c>
       <c r="D156" s="44" t="inlineStr">
@@ -12851,17 +12944,17 @@
     <row r="157">
       <c r="A157" s="44" t="inlineStr">
         <is>
-          <t>10. SEO &amp; CONTENT INTELLIGENCE  (SEO Agent, Market / Competitor Intelligence)</t>
+          <t>9. ANALYTICS, ATTRIBUTION &amp; REVENUE</t>
         </is>
       </c>
       <c r="B157" s="47" t="inlineStr">
         <is>
-          <t>TAVILY_API_KEY</t>
+          <t>BIGQUERY_PROJECT_ID</t>
         </is>
       </c>
       <c r="C157" s="50" t="inlineStr">
         <is>
-          <t>Tavily</t>
+          <t>Google Cloud (optional warehouse)</t>
         </is>
       </c>
       <c r="D157" s="44" t="inlineStr">
@@ -12878,17 +12971,17 @@
     <row r="158">
       <c r="A158" s="44" t="inlineStr">
         <is>
-          <t>10. SEO &amp; CONTENT INTELLIGENCE  (SEO Agent, Market / Competitor Intelligence)</t>
+          <t>9. ANALYTICS, ATTRIBUTION &amp; REVENUE</t>
         </is>
       </c>
       <c r="B158" s="47" t="inlineStr">
         <is>
-          <t>EXA_API_KEY</t>
+          <t>BIGQUERY_DATASET</t>
         </is>
       </c>
       <c r="C158" s="50" t="inlineStr">
         <is>
-          <t>Exa</t>
+          <t>Google Cloud (optional warehouse)</t>
         </is>
       </c>
       <c r="D158" s="44" t="inlineStr">
@@ -12905,17 +12998,17 @@
     <row r="159">
       <c r="A159" s="44" t="inlineStr">
         <is>
-          <t>10. SEO &amp; CONTENT INTELLIGENCE  (SEO Agent, Market / Competitor Intelligence)</t>
+          <t>9. ANALYTICS, ATTRIBUTION &amp; REVENUE</t>
         </is>
       </c>
       <c r="B159" s="47" t="inlineStr">
         <is>
-          <t>BRAVE_SEARCH_API_KEY</t>
+          <t>SNOWFLAKE_ACCOUNT</t>
         </is>
       </c>
       <c r="C159" s="50" t="inlineStr">
         <is>
-          <t>Brave Search (alternative to Tavily)</t>
+          <t>Snowflake (optional warehouse)</t>
         </is>
       </c>
       <c r="D159" s="44" t="inlineStr">
@@ -12932,17 +13025,17 @@
     <row r="160">
       <c r="A160" s="44" t="inlineStr">
         <is>
-          <t>10. SEO &amp; CONTENT INTELLIGENCE  (SEO Agent, Market / Competitor Intelligence)</t>
+          <t>9. ANALYTICS, ATTRIBUTION &amp; REVENUE</t>
         </is>
       </c>
       <c r="B160" s="47" t="inlineStr">
         <is>
-          <t>NEWSAPI_KEY</t>
+          <t>SNOWFLAKE_USER</t>
         </is>
       </c>
       <c r="C160" s="50" t="inlineStr">
         <is>
-          <t>NewsAPI</t>
+          <t>Snowflake (optional warehouse)</t>
         </is>
       </c>
       <c r="D160" s="44" t="inlineStr">
@@ -12959,17 +13052,17 @@
     <row r="161">
       <c r="A161" s="44" t="inlineStr">
         <is>
-          <t>10. SEO &amp; CONTENT INTELLIGENCE  (SEO Agent, Market / Competitor Intelligence)</t>
+          <t>9. ANALYTICS, ATTRIBUTION &amp; REVENUE</t>
         </is>
       </c>
       <c r="B161" s="47" t="inlineStr">
         <is>
-          <t>META_AD_LIBRARY_ACCESS_TOKEN</t>
+          <t>SNOWFLAKE_PASSWORD</t>
         </is>
       </c>
       <c r="C161" s="50" t="inlineStr">
         <is>
-          <t>Meta Ads (usually the same token)</t>
+          <t>Snowflake (optional warehouse)</t>
         </is>
       </c>
       <c r="D161" s="44" t="inlineStr">
@@ -12991,12 +13084,12 @@
       </c>
       <c r="B162" s="47" t="inlineStr">
         <is>
-          <t>WORDPRESS_URL</t>
+          <t>SEMRUSH_API_KEY</t>
         </is>
       </c>
       <c r="C162" s="50" t="inlineStr">
         <is>
-          <t>WordPress</t>
+          <t>Semrush</t>
         </is>
       </c>
       <c r="D162" s="44" t="inlineStr">
@@ -13018,12 +13111,12 @@
       </c>
       <c r="B163" s="47" t="inlineStr">
         <is>
-          <t>WORDPRESS_USERNAME</t>
+          <t>AHREFS_API_KEY</t>
         </is>
       </c>
       <c r="C163" s="50" t="inlineStr">
         <is>
-          <t>WordPress</t>
+          <t>Ahrefs</t>
         </is>
       </c>
       <c r="D163" s="44" t="inlineStr">
@@ -13045,12 +13138,12 @@
       </c>
       <c r="B164" s="47" t="inlineStr">
         <is>
-          <t>WORDPRESS_APP_PASSWORD</t>
+          <t>SERPAPI_API_KEY</t>
         </is>
       </c>
       <c r="C164" s="50" t="inlineStr">
         <is>
-          <t>WordPress</t>
+          <t>SerpApi</t>
         </is>
       </c>
       <c r="D164" s="44" t="inlineStr">
@@ -13072,12 +13165,12 @@
       </c>
       <c r="B165" s="47" t="inlineStr">
         <is>
-          <t>WEBFLOW_API_TOKEN</t>
+          <t>DATAFORSEO_LOGIN</t>
         </is>
       </c>
       <c r="C165" s="50" t="inlineStr">
         <is>
-          <t>Webflow</t>
+          <t>DataForSEO</t>
         </is>
       </c>
       <c r="D165" s="44" t="inlineStr">
@@ -13099,12 +13192,12 @@
       </c>
       <c r="B166" s="47" t="inlineStr">
         <is>
-          <t>WEBFLOW_SITE_ID</t>
+          <t>DATAFORSEO_PASSWORD</t>
         </is>
       </c>
       <c r="C166" s="50" t="inlineStr">
         <is>
-          <t>Webflow</t>
+          <t>DataForSEO</t>
         </is>
       </c>
       <c r="D166" s="44" t="inlineStr">
@@ -13121,17 +13214,17 @@
     <row r="167">
       <c r="A167" s="44" t="inlineStr">
         <is>
-          <t>11. LANDING PAGES / CRO / HOSTING</t>
+          <t>10. SEO &amp; CONTENT INTELLIGENCE  (SEO Agent, Market / Competitor Intelligence)</t>
         </is>
       </c>
       <c r="B167" s="47" t="inlineStr">
         <is>
-          <t>LANDING_PAGE_DOMAIN</t>
+          <t>FIRECRAWL_API_KEY</t>
         </is>
       </c>
       <c r="C167" s="50" t="inlineStr">
         <is>
-          <t>Vercel</t>
+          <t>Firecrawl</t>
         </is>
       </c>
       <c r="D167" s="44" t="inlineStr">
@@ -13148,17 +13241,17 @@
     <row r="168">
       <c r="A168" s="44" t="inlineStr">
         <is>
-          <t>11. LANDING PAGES / CRO / HOSTING</t>
+          <t>10. SEO &amp; CONTENT INTELLIGENCE  (SEO Agent, Market / Competitor Intelligence)</t>
         </is>
       </c>
       <c r="B168" s="47" t="inlineStr">
         <is>
-          <t>VERCEL_TOKEN</t>
+          <t>TAVILY_API_KEY</t>
         </is>
       </c>
       <c r="C168" s="50" t="inlineStr">
         <is>
-          <t>Vercel</t>
+          <t>Tavily</t>
         </is>
       </c>
       <c r="D168" s="44" t="inlineStr">
@@ -13175,17 +13268,17 @@
     <row r="169">
       <c r="A169" s="44" t="inlineStr">
         <is>
-          <t>11. LANDING PAGES / CRO / HOSTING</t>
+          <t>10. SEO &amp; CONTENT INTELLIGENCE  (SEO Agent, Market / Competitor Intelligence)</t>
         </is>
       </c>
       <c r="B169" s="47" t="inlineStr">
         <is>
-          <t>VERCEL_PROJECT_ID</t>
+          <t>EXA_API_KEY</t>
         </is>
       </c>
       <c r="C169" s="50" t="inlineStr">
         <is>
-          <t>Vercel</t>
+          <t>Exa</t>
         </is>
       </c>
       <c r="D169" s="44" t="inlineStr">
@@ -13202,17 +13295,17 @@
     <row r="170">
       <c r="A170" s="44" t="inlineStr">
         <is>
-          <t>11. LANDING PAGES / CRO / HOSTING</t>
+          <t>10. SEO &amp; CONTENT INTELLIGENCE  (SEO Agent, Market / Competitor Intelligence)</t>
         </is>
       </c>
       <c r="B170" s="47" t="inlineStr">
         <is>
-          <t>CLOUDFLARE_API_TOKEN</t>
+          <t>BRAVE_SEARCH_API_KEY</t>
         </is>
       </c>
       <c r="C170" s="50" t="inlineStr">
         <is>
-          <t>Cloudflare (DNS for landing pages)</t>
+          <t>Brave Search (alternative to Tavily)</t>
         </is>
       </c>
       <c r="D170" s="44" t="inlineStr">
@@ -13229,17 +13322,17 @@
     <row r="171">
       <c r="A171" s="44" t="inlineStr">
         <is>
-          <t>11. LANDING PAGES / CRO / HOSTING</t>
+          <t>10. SEO &amp; CONTENT INTELLIGENCE  (SEO Agent, Market / Competitor Intelligence)</t>
         </is>
       </c>
       <c r="B171" s="47" t="inlineStr">
         <is>
-          <t>CLOUDFLARE_ZONE_ID</t>
+          <t>NEWSAPI_KEY</t>
         </is>
       </c>
       <c r="C171" s="50" t="inlineStr">
         <is>
-          <t>Cloudflare (DNS for landing pages)</t>
+          <t>NewsAPI</t>
         </is>
       </c>
       <c r="D171" s="44" t="inlineStr">
@@ -13256,17 +13349,17 @@
     <row r="172">
       <c r="A172" s="44" t="inlineStr">
         <is>
-          <t>11. LANDING PAGES / CRO / HOSTING</t>
+          <t>10. SEO &amp; CONTENT INTELLIGENCE  (SEO Agent, Market / Competitor Intelligence)</t>
         </is>
       </c>
       <c r="B172" s="47" t="inlineStr">
         <is>
-          <t>VWO_ACCOUNT_ID</t>
+          <t>META_AD_LIBRARY_ACCESS_TOKEN</t>
         </is>
       </c>
       <c r="C172" s="50" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>Meta Ads (usually the same token)</t>
         </is>
       </c>
       <c r="D172" s="44" t="inlineStr">
@@ -13283,17 +13376,17 @@
     <row r="173">
       <c r="A173" s="44" t="inlineStr">
         <is>
-          <t>11. LANDING PAGES / CRO / HOSTING</t>
+          <t>10. SEO &amp; CONTENT INTELLIGENCE  (SEO Agent, Market / Competitor Intelligence)</t>
         </is>
       </c>
       <c r="B173" s="47" t="inlineStr">
         <is>
-          <t>VWO_API_TOKEN</t>
+          <t>WORDPRESS_URL</t>
         </is>
       </c>
       <c r="C173" s="50" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>WordPress</t>
         </is>
       </c>
       <c r="D173" s="44" t="inlineStr">
@@ -13310,17 +13403,17 @@
     <row r="174">
       <c r="A174" s="44" t="inlineStr">
         <is>
-          <t>11. LANDING PAGES / CRO / HOSTING</t>
+          <t>10. SEO &amp; CONTENT INTELLIGENCE  (SEO Agent, Market / Competitor Intelligence)</t>
         </is>
       </c>
       <c r="B174" s="47" t="inlineStr">
         <is>
-          <t>HOTJAR_SITE_ID</t>
+          <t>WORDPRESS_USERNAME</t>
         </is>
       </c>
       <c r="C174" s="50" t="inlineStr">
         <is>
-          <t>Hotjar (optional heatmaps)</t>
+          <t>WordPress</t>
         </is>
       </c>
       <c r="D174" s="44" t="inlineStr">
@@ -13337,17 +13430,17 @@
     <row r="175">
       <c r="A175" s="44" t="inlineStr">
         <is>
-          <t>11. LANDING PAGES / CRO / HOSTING</t>
+          <t>10. SEO &amp; CONTENT INTELLIGENCE  (SEO Agent, Market / Competitor Intelligence)</t>
         </is>
       </c>
       <c r="B175" s="47" t="inlineStr">
         <is>
-          <t>MICROSOFT_CLARITY_PROJECT_ID</t>
+          <t>WORDPRESS_APP_PASSWORD</t>
         </is>
       </c>
       <c r="C175" s="50" t="inlineStr">
         <is>
-          <t>Microsoft Clarity (free heatmaps)</t>
+          <t>WordPress</t>
         </is>
       </c>
       <c r="D175" s="44" t="inlineStr">
@@ -13364,17 +13457,17 @@
     <row r="176">
       <c r="A176" s="44" t="inlineStr">
         <is>
-          <t>12. STORAGE, QUEUES &amp; OBSERVABILITY</t>
+          <t>10. SEO &amp; CONTENT INTELLIGENCE  (SEO Agent, Market / Competitor Intelligence)</t>
         </is>
       </c>
       <c r="B176" s="47" t="inlineStr">
         <is>
-          <t>STORAGE_BACKEND</t>
+          <t>WEBFLOW_API_TOKEN</t>
         </is>
       </c>
       <c r="C176" s="50" t="inlineStr">
         <is>
-          <t>AWS S3 / Cloudflare R2</t>
+          <t>Webflow</t>
         </is>
       </c>
       <c r="D176" s="44" t="inlineStr">
@@ -13391,17 +13484,17 @@
     <row r="177">
       <c r="A177" s="44" t="inlineStr">
         <is>
-          <t>12. STORAGE, QUEUES &amp; OBSERVABILITY</t>
+          <t>10. SEO &amp; CONTENT INTELLIGENCE  (SEO Agent, Market / Competitor Intelligence)</t>
         </is>
       </c>
       <c r="B177" s="47" t="inlineStr">
         <is>
-          <t>AWS_ACCESS_KEY_ID</t>
+          <t>WEBFLOW_SITE_ID</t>
         </is>
       </c>
       <c r="C177" s="50" t="inlineStr">
         <is>
-          <t>AWS S3 / Cloudflare R2</t>
+          <t>Webflow</t>
         </is>
       </c>
       <c r="D177" s="44" t="inlineStr">
@@ -13418,17 +13511,17 @@
     <row r="178">
       <c r="A178" s="44" t="inlineStr">
         <is>
-          <t>12. STORAGE, QUEUES &amp; OBSERVABILITY</t>
+          <t>11. LANDING PAGES / CRO / HOSTING</t>
         </is>
       </c>
       <c r="B178" s="47" t="inlineStr">
         <is>
-          <t>AWS_SECRET_ACCESS_KEY</t>
+          <t>LANDING_PAGE_DOMAIN</t>
         </is>
       </c>
       <c r="C178" s="50" t="inlineStr">
         <is>
-          <t>AWS S3 / Cloudflare R2</t>
+          <t>Vercel</t>
         </is>
       </c>
       <c r="D178" s="44" t="inlineStr">
@@ -13445,17 +13538,17 @@
     <row r="179">
       <c r="A179" s="44" t="inlineStr">
         <is>
-          <t>12. STORAGE, QUEUES &amp; OBSERVABILITY</t>
+          <t>11. LANDING PAGES / CRO / HOSTING</t>
         </is>
       </c>
       <c r="B179" s="47" t="inlineStr">
         <is>
-          <t>AWS_STORAGE_BUCKET_NAME</t>
+          <t>VERCEL_TOKEN</t>
         </is>
       </c>
       <c r="C179" s="50" t="inlineStr">
         <is>
-          <t>AWS S3 / Cloudflare R2</t>
+          <t>Vercel</t>
         </is>
       </c>
       <c r="D179" s="44" t="inlineStr">
@@ -13472,17 +13565,17 @@
     <row r="180">
       <c r="A180" s="44" t="inlineStr">
         <is>
-          <t>12. STORAGE, QUEUES &amp; OBSERVABILITY</t>
+          <t>11. LANDING PAGES / CRO / HOSTING</t>
         </is>
       </c>
       <c r="B180" s="47" t="inlineStr">
         <is>
-          <t>AWS_S3_REGION_NAME</t>
+          <t>VERCEL_PROJECT_ID</t>
         </is>
       </c>
       <c r="C180" s="50" t="inlineStr">
         <is>
-          <t>AWS S3 / Cloudflare R2</t>
+          <t>Vercel</t>
         </is>
       </c>
       <c r="D180" s="44" t="inlineStr">
@@ -13499,17 +13592,17 @@
     <row r="181">
       <c r="A181" s="44" t="inlineStr">
         <is>
-          <t>12. STORAGE, QUEUES &amp; OBSERVABILITY</t>
+          <t>11. LANDING PAGES / CRO / HOSTING</t>
         </is>
       </c>
       <c r="B181" s="47" t="inlineStr">
         <is>
-          <t>R2_ACCOUNT_ID</t>
+          <t>CLOUDFLARE_API_TOKEN</t>
         </is>
       </c>
       <c r="C181" s="50" t="inlineStr">
         <is>
-          <t>Cloudflare R2 (storage)</t>
+          <t>Cloudflare (DNS for landing pages)</t>
         </is>
       </c>
       <c r="D181" s="44" t="inlineStr">
@@ -13526,17 +13619,17 @@
     <row r="182">
       <c r="A182" s="44" t="inlineStr">
         <is>
-          <t>12. STORAGE, QUEUES &amp; OBSERVABILITY</t>
+          <t>11. LANDING PAGES / CRO / HOSTING</t>
         </is>
       </c>
       <c r="B182" s="47" t="inlineStr">
         <is>
-          <t>SENTRY_DSN</t>
+          <t>CLOUDFLARE_ZONE_ID</t>
         </is>
       </c>
       <c r="C182" s="50" t="inlineStr">
         <is>
-          <t>Sentry</t>
+          <t>Cloudflare (DNS for landing pages)</t>
         </is>
       </c>
       <c r="D182" s="44" t="inlineStr">
@@ -13553,44 +13646,44 @@
     <row r="183">
       <c r="A183" s="44" t="inlineStr">
         <is>
-          <t>12. STORAGE, QUEUES &amp; OBSERVABILITY</t>
+          <t>11. LANDING PAGES / CRO / HOSTING</t>
         </is>
       </c>
       <c r="B183" s="47" t="inlineStr">
         <is>
-          <t>LOG_LEVEL</t>
-        </is>
-      </c>
-      <c r="C183" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>VWO_ACCOUNT_ID</t>
+        </is>
+      </c>
+      <c r="C183" s="50" t="inlineStr">
+        <is>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D183" s="44" t="inlineStr">
         <is>
-          <t>Platform setting</t>
+          <t>Provider credential</t>
         </is>
       </c>
       <c r="E183" s="44" t="inlineStr">
         <is>
-          <t>Has a default</t>
+          <t>No — simulates if blank</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="44" t="inlineStr">
         <is>
-          <t>12. STORAGE, QUEUES &amp; OBSERVABILITY</t>
+          <t>11. LANDING PAGES / CRO / HOSTING</t>
         </is>
       </c>
       <c r="B184" s="47" t="inlineStr">
         <is>
-          <t>SLACK_BOT_TOKEN</t>
+          <t>VWO_API_TOKEN</t>
         </is>
       </c>
       <c r="C184" s="50" t="inlineStr">
         <is>
-          <t>Slack</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="D184" s="44" t="inlineStr">
@@ -13607,17 +13700,17 @@
     <row r="185">
       <c r="A185" s="44" t="inlineStr">
         <is>
-          <t>12. STORAGE, QUEUES &amp; OBSERVABILITY</t>
+          <t>11. LANDING PAGES / CRO / HOSTING</t>
         </is>
       </c>
       <c r="B185" s="47" t="inlineStr">
         <is>
-          <t>SLACK_ALERTS_CHANNEL</t>
+          <t>HOTJAR_SITE_ID</t>
         </is>
       </c>
       <c r="C185" s="50" t="inlineStr">
         <is>
-          <t>Slack</t>
+          <t>Hotjar (optional heatmaps)</t>
         </is>
       </c>
       <c r="D185" s="44" t="inlineStr">
@@ -13634,17 +13727,17 @@
     <row r="186">
       <c r="A186" s="44" t="inlineStr">
         <is>
-          <t>12. STORAGE, QUEUES &amp; OBSERVABILITY</t>
+          <t>11. LANDING PAGES / CRO / HOSTING</t>
         </is>
       </c>
       <c r="B186" s="47" t="inlineStr">
         <is>
-          <t>SLACK_SIGNING_SECRET</t>
+          <t>MICROSOFT_CLARITY_PROJECT_ID</t>
         </is>
       </c>
       <c r="C186" s="50" t="inlineStr">
         <is>
-          <t>Slack</t>
+          <t>Microsoft Clarity (free heatmaps)</t>
         </is>
       </c>
       <c r="D186" s="44" t="inlineStr">
@@ -13661,201 +13754,201 @@
     <row r="187">
       <c r="A187" s="44" t="inlineStr">
         <is>
-          <t>13. HUMAN CONTROL DEFAULTS  (overridable per workspace in Settings)</t>
+          <t>12. STORAGE, QUEUES &amp; OBSERVABILITY</t>
         </is>
       </c>
       <c r="B187" s="47" t="inlineStr">
         <is>
-          <t>DEFAULT_CONTROL_MODE</t>
-        </is>
-      </c>
-      <c r="C187" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>STORAGE_BACKEND</t>
+        </is>
+      </c>
+      <c r="C187" s="50" t="inlineStr">
+        <is>
+          <t>AWS S3 / Cloudflare R2</t>
         </is>
       </c>
       <c r="D187" s="44" t="inlineStr">
         <is>
-          <t>Platform setting</t>
+          <t>Provider credential</t>
         </is>
       </c>
       <c r="E187" s="44" t="inlineStr">
         <is>
-          <t>Has a default</t>
+          <t>No — simulates if blank</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="44" t="inlineStr">
         <is>
-          <t>13. HUMAN CONTROL DEFAULTS  (overridable per workspace in Settings)</t>
+          <t>12. STORAGE, QUEUES &amp; OBSERVABILITY</t>
         </is>
       </c>
       <c r="B188" s="47" t="inlineStr">
         <is>
-          <t>DEFAULT_DAILY_SPEND_CAP</t>
-        </is>
-      </c>
-      <c r="C188" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>AWS_ACCESS_KEY_ID</t>
+        </is>
+      </c>
+      <c r="C188" s="50" t="inlineStr">
+        <is>
+          <t>AWS S3 / Cloudflare R2</t>
         </is>
       </c>
       <c r="D188" s="44" t="inlineStr">
         <is>
-          <t>Platform setting</t>
+          <t>Provider credential</t>
         </is>
       </c>
       <c r="E188" s="44" t="inlineStr">
         <is>
-          <t>Has a default</t>
+          <t>No — simulates if blank</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="44" t="inlineStr">
         <is>
-          <t>13. HUMAN CONTROL DEFAULTS  (overridable per workspace in Settings)</t>
+          <t>12. STORAGE, QUEUES &amp; OBSERVABILITY</t>
         </is>
       </c>
       <c r="B189" s="47" t="inlineStr">
         <is>
-          <t>DEFAULT_CURRENCY</t>
-        </is>
-      </c>
-      <c r="C189" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>AWS_SECRET_ACCESS_KEY</t>
+        </is>
+      </c>
+      <c r="C189" s="50" t="inlineStr">
+        <is>
+          <t>AWS S3 / Cloudflare R2</t>
         </is>
       </c>
       <c r="D189" s="44" t="inlineStr">
         <is>
-          <t>Platform setting</t>
+          <t>Provider credential</t>
         </is>
       </c>
       <c r="E189" s="44" t="inlineStr">
         <is>
-          <t>Has a default</t>
+          <t>No — simulates if blank</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="44" t="inlineStr">
         <is>
-          <t>13. HUMAN CONTROL DEFAULTS  (overridable per workspace in Settings)</t>
+          <t>12. STORAGE, QUEUES &amp; OBSERVABILITY</t>
         </is>
       </c>
       <c r="B190" s="47" t="inlineStr">
         <is>
-          <t>AI_CAN_CHANGE_PRICING</t>
-        </is>
-      </c>
-      <c r="C190" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>AWS_STORAGE_BUCKET_NAME</t>
+        </is>
+      </c>
+      <c r="C190" s="50" t="inlineStr">
+        <is>
+          <t>AWS S3 / Cloudflare R2</t>
         </is>
       </c>
       <c r="D190" s="44" t="inlineStr">
         <is>
-          <t>Platform setting</t>
+          <t>Provider credential</t>
         </is>
       </c>
       <c r="E190" s="44" t="inlineStr">
         <is>
-          <t>Has a default</t>
+          <t>No — simulates if blank</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="44" t="inlineStr">
         <is>
-          <t>13. HUMAN CONTROL DEFAULTS  (overridable per workspace in Settings)</t>
+          <t>12. STORAGE, QUEUES &amp; OBSERVABILITY</t>
         </is>
       </c>
       <c r="B191" s="47" t="inlineStr">
         <is>
-          <t>AI_CAN_EMAIL_UNAPPROVED_ICPS</t>
-        </is>
-      </c>
-      <c r="C191" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>AWS_S3_REGION_NAME</t>
+        </is>
+      </c>
+      <c r="C191" s="50" t="inlineStr">
+        <is>
+          <t>AWS S3 / Cloudflare R2</t>
         </is>
       </c>
       <c r="D191" s="44" t="inlineStr">
         <is>
-          <t>Platform setting</t>
+          <t>Provider credential</t>
         </is>
       </c>
       <c r="E191" s="44" t="inlineStr">
         <is>
-          <t>Has a default</t>
+          <t>No — simulates if blank</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="44" t="inlineStr">
         <is>
-          <t>13. HUMAN CONTROL DEFAULTS  (overridable per workspace in Settings)</t>
+          <t>12. STORAGE, QUEUES &amp; OBSERVABILITY</t>
         </is>
       </c>
       <c r="B192" s="47" t="inlineStr">
         <is>
-          <t>COMPLIANCE_GATE_REQUIRED</t>
-        </is>
-      </c>
-      <c r="C192" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>R2_ACCOUNT_ID</t>
+        </is>
+      </c>
+      <c r="C192" s="50" t="inlineStr">
+        <is>
+          <t>Cloudflare R2 (storage)</t>
         </is>
       </c>
       <c r="D192" s="44" t="inlineStr">
         <is>
-          <t>Platform setting</t>
+          <t>Provider credential</t>
         </is>
       </c>
       <c r="E192" s="44" t="inlineStr">
         <is>
-          <t>Has a default</t>
+          <t>No — simulates if blank</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="44" t="inlineStr">
         <is>
-          <t>13. HUMAN CONTROL DEFAULTS  (overridable per workspace in Settings)</t>
+          <t>12. STORAGE, QUEUES &amp; OBSERVABILITY</t>
         </is>
       </c>
       <c r="B193" s="47" t="inlineStr">
         <is>
-          <t>REGULATED_VERTICAL</t>
-        </is>
-      </c>
-      <c r="C193" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>SENTRY_DSN</t>
+        </is>
+      </c>
+      <c r="C193" s="50" t="inlineStr">
+        <is>
+          <t>Sentry</t>
         </is>
       </c>
       <c r="D193" s="44" t="inlineStr">
         <is>
-          <t>Platform setting</t>
+          <t>Provider credential</t>
         </is>
       </c>
       <c r="E193" s="44" t="inlineStr">
         <is>
-          <t>Has a default</t>
+          <t>No — simulates if blank</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="44" t="inlineStr">
         <is>
-          <t>14. FRONTEND  (Vite reads only VITE_* vars - these live in frontend/.env)</t>
+          <t>12. STORAGE, QUEUES &amp; OBSERVABILITY</t>
         </is>
       </c>
       <c r="B194" s="47" t="inlineStr">
         <is>
-          <t>VITE_API_URL</t>
+          <t>LOG_LEVEL</t>
         </is>
       </c>
       <c r="C194" s="48" t="inlineStr">
@@ -13865,7 +13958,7 @@
       </c>
       <c r="D194" s="44" t="inlineStr">
         <is>
-          <t>Frontend setting</t>
+          <t>Platform setting</t>
         </is>
       </c>
       <c r="E194" s="44" t="inlineStr">
@@ -13877,86 +13970,383 @@
     <row r="195">
       <c r="A195" s="44" t="inlineStr">
         <is>
-          <t>14. FRONTEND  (Vite reads only VITE_* vars - these live in frontend/.env)</t>
+          <t>12. STORAGE, QUEUES &amp; OBSERVABILITY</t>
         </is>
       </c>
       <c r="B195" s="47" t="inlineStr">
         <is>
-          <t>VITE_APP_NAME</t>
-        </is>
-      </c>
-      <c r="C195" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>SLACK_BOT_TOKEN</t>
+        </is>
+      </c>
+      <c r="C195" s="50" t="inlineStr">
+        <is>
+          <t>Slack</t>
         </is>
       </c>
       <c r="D195" s="44" t="inlineStr">
         <is>
-          <t>Frontend setting</t>
+          <t>Provider credential</t>
         </is>
       </c>
       <c r="E195" s="44" t="inlineStr">
         <is>
-          <t>Has a default</t>
+          <t>No — simulates if blank</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="44" t="inlineStr">
         <is>
-          <t>14. FRONTEND  (Vite reads only VITE_* vars - these live in frontend/.env)</t>
+          <t>12. STORAGE, QUEUES &amp; OBSERVABILITY</t>
         </is>
       </c>
       <c r="B196" s="47" t="inlineStr">
         <is>
-          <t>VITE_DEMO_EMAIL</t>
-        </is>
-      </c>
-      <c r="C196" s="48" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>SLACK_ALERTS_CHANNEL</t>
+        </is>
+      </c>
+      <c r="C196" s="50" t="inlineStr">
+        <is>
+          <t>Slack</t>
         </is>
       </c>
       <c r="D196" s="44" t="inlineStr">
         <is>
-          <t>Frontend setting</t>
+          <t>Provider credential</t>
         </is>
       </c>
       <c r="E196" s="44" t="inlineStr">
         <is>
-          <t>Has a default</t>
+          <t>No — simulates if blank</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="44" t="inlineStr">
         <is>
+          <t>12. STORAGE, QUEUES &amp; OBSERVABILITY</t>
+        </is>
+      </c>
+      <c r="B197" s="47" t="inlineStr">
+        <is>
+          <t>SLACK_SIGNING_SECRET</t>
+        </is>
+      </c>
+      <c r="C197" s="50" t="inlineStr">
+        <is>
+          <t>Slack</t>
+        </is>
+      </c>
+      <c r="D197" s="44" t="inlineStr">
+        <is>
+          <t>Provider credential</t>
+        </is>
+      </c>
+      <c r="E197" s="44" t="inlineStr">
+        <is>
+          <t>No — simulates if blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="44" t="inlineStr">
+        <is>
+          <t>13. HUMAN CONTROL DEFAULTS  (overridable per workspace in Settings)</t>
+        </is>
+      </c>
+      <c r="B198" s="47" t="inlineStr">
+        <is>
+          <t>DEFAULT_CONTROL_MODE</t>
+        </is>
+      </c>
+      <c r="C198" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D198" s="44" t="inlineStr">
+        <is>
+          <t>Platform setting</t>
+        </is>
+      </c>
+      <c r="E198" s="44" t="inlineStr">
+        <is>
+          <t>Has a default</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="44" t="inlineStr">
+        <is>
+          <t>13. HUMAN CONTROL DEFAULTS  (overridable per workspace in Settings)</t>
+        </is>
+      </c>
+      <c r="B199" s="47" t="inlineStr">
+        <is>
+          <t>DEFAULT_DAILY_SPEND_CAP</t>
+        </is>
+      </c>
+      <c r="C199" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D199" s="44" t="inlineStr">
+        <is>
+          <t>Platform setting</t>
+        </is>
+      </c>
+      <c r="E199" s="44" t="inlineStr">
+        <is>
+          <t>Has a default</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="44" t="inlineStr">
+        <is>
+          <t>13. HUMAN CONTROL DEFAULTS  (overridable per workspace in Settings)</t>
+        </is>
+      </c>
+      <c r="B200" s="47" t="inlineStr">
+        <is>
+          <t>DEFAULT_CURRENCY</t>
+        </is>
+      </c>
+      <c r="C200" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D200" s="44" t="inlineStr">
+        <is>
+          <t>Platform setting</t>
+        </is>
+      </c>
+      <c r="E200" s="44" t="inlineStr">
+        <is>
+          <t>Has a default</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="44" t="inlineStr">
+        <is>
+          <t>13. HUMAN CONTROL DEFAULTS  (overridable per workspace in Settings)</t>
+        </is>
+      </c>
+      <c r="B201" s="47" t="inlineStr">
+        <is>
+          <t>AI_CAN_CHANGE_PRICING</t>
+        </is>
+      </c>
+      <c r="C201" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D201" s="44" t="inlineStr">
+        <is>
+          <t>Platform setting</t>
+        </is>
+      </c>
+      <c r="E201" s="44" t="inlineStr">
+        <is>
+          <t>Has a default</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="44" t="inlineStr">
+        <is>
+          <t>13. HUMAN CONTROL DEFAULTS  (overridable per workspace in Settings)</t>
+        </is>
+      </c>
+      <c r="B202" s="47" t="inlineStr">
+        <is>
+          <t>AI_CAN_EMAIL_UNAPPROVED_ICPS</t>
+        </is>
+      </c>
+      <c r="C202" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D202" s="44" t="inlineStr">
+        <is>
+          <t>Platform setting</t>
+        </is>
+      </c>
+      <c r="E202" s="44" t="inlineStr">
+        <is>
+          <t>Has a default</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="44" t="inlineStr">
+        <is>
+          <t>13. HUMAN CONTROL DEFAULTS  (overridable per workspace in Settings)</t>
+        </is>
+      </c>
+      <c r="B203" s="47" t="inlineStr">
+        <is>
+          <t>COMPLIANCE_GATE_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C203" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D203" s="44" t="inlineStr">
+        <is>
+          <t>Platform setting</t>
+        </is>
+      </c>
+      <c r="E203" s="44" t="inlineStr">
+        <is>
+          <t>Has a default</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="44" t="inlineStr">
+        <is>
+          <t>13. HUMAN CONTROL DEFAULTS  (overridable per workspace in Settings)</t>
+        </is>
+      </c>
+      <c r="B204" s="47" t="inlineStr">
+        <is>
+          <t>REGULATED_VERTICAL</t>
+        </is>
+      </c>
+      <c r="C204" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D204" s="44" t="inlineStr">
+        <is>
+          <t>Platform setting</t>
+        </is>
+      </c>
+      <c r="E204" s="44" t="inlineStr">
+        <is>
+          <t>Has a default</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="44" t="inlineStr">
+        <is>
           <t>14. FRONTEND  (Vite reads only VITE_* vars - these live in frontend/.env)</t>
         </is>
       </c>
-      <c r="B197" s="47" t="inlineStr">
+      <c r="B205" s="47" t="inlineStr">
+        <is>
+          <t>VITE_API_URL</t>
+        </is>
+      </c>
+      <c r="C205" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D205" s="44" t="inlineStr">
+        <is>
+          <t>Frontend setting</t>
+        </is>
+      </c>
+      <c r="E205" s="44" t="inlineStr">
+        <is>
+          <t>Has a default</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="44" t="inlineStr">
+        <is>
+          <t>14. FRONTEND  (Vite reads only VITE_* vars - these live in frontend/.env)</t>
+        </is>
+      </c>
+      <c r="B206" s="47" t="inlineStr">
+        <is>
+          <t>VITE_APP_NAME</t>
+        </is>
+      </c>
+      <c r="C206" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D206" s="44" t="inlineStr">
+        <is>
+          <t>Frontend setting</t>
+        </is>
+      </c>
+      <c r="E206" s="44" t="inlineStr">
+        <is>
+          <t>Has a default</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="44" t="inlineStr">
+        <is>
+          <t>14. FRONTEND  (Vite reads only VITE_* vars - these live in frontend/.env)</t>
+        </is>
+      </c>
+      <c r="B207" s="47" t="inlineStr">
+        <is>
+          <t>VITE_DEMO_EMAIL</t>
+        </is>
+      </c>
+      <c r="C207" s="48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D207" s="44" t="inlineStr">
+        <is>
+          <t>Frontend setting</t>
+        </is>
+      </c>
+      <c r="E207" s="44" t="inlineStr">
+        <is>
+          <t>Has a default</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="44" t="inlineStr">
+        <is>
+          <t>14. FRONTEND  (Vite reads only VITE_* vars - these live in frontend/.env)</t>
+        </is>
+      </c>
+      <c r="B208" s="47" t="inlineStr">
         <is>
           <t>VITE_DEMO_PASSWORD</t>
         </is>
       </c>
-      <c r="C197" s="48" t="inlineStr">
+      <c r="C208" s="48" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D197" s="44" t="inlineStr">
+      <c r="D208" s="44" t="inlineStr">
         <is>
           <t>Frontend setting</t>
         </is>
       </c>
-      <c r="E197" s="44" t="inlineStr">
+      <c r="E208" s="44" t="inlineStr">
         <is>
           <t>Has a default</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E197"/>
+  <autoFilter ref="A4:E208"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
